--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WA Pending (send after unban)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-REPLIED (send first)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-NEVER contacted (cold)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-CONTACTED on old number" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +42,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,9 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,16 +437,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,107 +461,242 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>History</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>IG Handle</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L007</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Golden Kyu Barcelona</t>
+          <t>Team Duramuk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>351967734557</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+34670425918</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>info@goldenkyu.com</t>
+          <t>Conversation existed on old number</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>@goldenkyu_bcn</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG followed + IG DM + WA + email sent</t>
+          <t>REPLIED before - re-contact first</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L078</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kick Barcelona</t>
+          <t>Scorpion Boxing Milano</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>393514088140</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+34635541239</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kickbarcelona@gmail.com</t>
+          <t>Conversation existed on old number</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>@kickbarcelona</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG followed + IG DM + email + WA sent (email re-co</t>
+          <t>REPLIED before - re-contact first</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>L074</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lucero Muay Thai Madrid</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>34633215305</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Conversation existed on old number</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>REPLIED before - re-contact first</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Lead ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>IG Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Golden Kyu Barcelona</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>+34670425918</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>info@goldenkyu.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>@goldenkyu_bcn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kick Barcelona</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>+34635541239</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kickbarcelona@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>@kickbarcelona</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>L003</t>
         </is>
       </c>
@@ -559,14 +707,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>+34620953033</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+34620953033</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>hola@warriorsbarcelona.com</t>
@@ -575,1242 +723,1938 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>@warriorsbarcelona</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>COMPLETE: already-following + IG DM + email + WA sent (email</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L007</t>
+          <t>L020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Invicta Martial Arts</t>
+          <t>Ippon Gear España</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>34611612163</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>351910479457</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>info@invictamaa.com</t>
+          <t>info@ippongear.es</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>@invictamaa</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=ok dm=sent email=sent wa={"ok":true,"last":</t>
+          <t>@ippongear_spain</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L020</t>
+          <t>L021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ippon Gear España</t>
+          <t>Splinters Jiu-Jitsu &amp; MMA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>34622212369</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>34611612163</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>info@ippongear.es</t>
+          <t>splintersmadrid@gmail.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>@ippongear_spain</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=ok dm=sent email=sent wa={"ok":true,"last":</t>
+          <t>@splintersmadrid</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L021</t>
+          <t>L023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Splinters Jiu-Jitsu &amp; MMA</t>
+          <t>Al-Andalus Judo Sevilla</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>34625621710</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>34622212369</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>splintersmadrid@gmail.com</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>@splintersmadrid</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
-        </is>
-      </c>
+          <t>info@judosevilla.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L023</t>
+          <t>L024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al-Andalus Judo Sevilla</t>
+          <t>KALMMA Fight Club</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>34699506391</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>34625621710</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>info@judosevilla.com</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last</t>
+          <t>info@kalmmafightclub.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>@kalmmafightclub</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L024</t>
+          <t>L025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KALMMA Fight Club</t>
+          <t>Judo Kitaro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>34649036805</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>34699506391</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>info@kalmmafightclub.com</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>@kalmmafightclub</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG DM sent (follow btn n/a - already following)</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L025</t>
+          <t>L026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Judo Kitaro</t>
+          <t>Brazilian Fight Lisboa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>351910349061</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34649036805</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last</t>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>brazilian.fight.lisboa@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>@brazilian.fight.lisboa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L026</t>
+          <t>L027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brazilian Fight Lisboa</t>
+          <t>K.O. Team Portugal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>351963919855</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>351910349061</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>brazilian.fight.lisboa@gmail.com</t>
+          <t>info@koteam.pt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>@brazilian.fight.lisboa</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=no-btn dm=sent email=sent wa={"ok":true,"la</t>
+          <t>@koteamportugal</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L027</t>
+          <t>L028</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K.O. Team Portugal</t>
+          <t>Team Duramuk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>351967734557</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>351963919855</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>info@koteam.pt</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>@koteamportugal</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG followed + IG DM sent + email sent (info@koteam</t>
+          <t>@team.duramuk</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L028</t>
+          <t>L029</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Duramuk</t>
+          <t>Five Elements Academy Jiu-Jitsu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>351915267080</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>351967734557</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>@team.duramuk</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG followed + IG DM + WA sent (no public email - W</t>
+          <t>@fiveelementsjiujitsu</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L029</t>
+          <t>L030</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Five Elements Academy Jiu-Jitsu</t>
+          <t>Gracie Lisboa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>351967599340</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>351915267080</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>@fiveelementsjiujitsu</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L030</t>
+          <t>L031</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gracie Lisboa</t>
+          <t>APKO Okinawa Karate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>351961320560</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>351967599340</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>apko.geral@gmail.com</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L031</t>
+          <t>L054</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APKO Okinawa Karate</t>
+          <t>FullGym 24h Vilafranca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>34621413059</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>351961320560</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>apko.geral@gmail.com</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last</t>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>@fullgymvilafranca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L054</t>
+          <t>L132</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FullGym 24h Vilafranca</t>
+          <t>Alvaro Campeao</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>351916033601</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34621413059</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pt.alvarocampeao@gmail.com</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>@fullgymvilafranca</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=ok dm=sent email=None wa={"ok":true,"last":</t>
+          <t>@alvarotdcampeao</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L132</t>
+          <t>L140</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alvaro Campeao</t>
+          <t>Fight Center Boxing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>33783401554</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>351916033601</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>pt.alvarocampeao@gmail.com</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>@alvarotdcampeao</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent + IG followed + IG DM sent (phone NOT o</t>
-        </is>
-      </c>
+          <t>fightboxing13@gmail.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L140</t>
+          <t>L144</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fight Center Boxing</t>
+          <t>Angels Boxing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>353873256588</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33783401554</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>fightboxing13@gmail.com</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent (phone NOT on WhatsApp — verified)</t>
+          <t>byrnereg43@gmail.com</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>@coach_reg.byrne</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L144</t>
+          <t>L153</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Angels Boxing</t>
+          <t>Bomaye Gym München</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>491737513627</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>353873256588</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>byrnereg43@gmail.com</t>
-        </is>
-      </c>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>@coach_reg.byrne</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=no-btn dm=sent email=recipient-not-register</t>
+          <t>@bomayegym_munich</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L153</t>
+          <t>L154</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bomaye Gym München</t>
+          <t>Martial Arts Center München</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>491708890687</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>491737513627</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>@bomayegym_munich</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=clicked dm=sent email=None wa=no-composer</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>info@ving-tsun.net</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L154</t>
+          <t>L158</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Martial Arts Center München</t>
+          <t>Crossbox Gym</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>34649316067</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>491708890687</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>info@ving-tsun.net</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa=no-composer</t>
+          <t>crossboxgym@protonmail.com</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>@crossboxgym</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L158</t>
+          <t>L159</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crossbox Gym</t>
+          <t>Ali Promotions BCN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>34687075304</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>34649316067</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>crossboxgym@protonmail.com</t>
+          <t>alipromotions.bcn@gmail.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>@crossboxgym</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=no-btn dm=sent email=sent wa=no-composer</t>
+          <t>@alipromotions.bcn</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L159</t>
+          <t>L160</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ali Promotions BCN</t>
+          <t>Hybrd Academy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>34692382544</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>34687075304</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>alipromotions.bcn@gmail.com</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>@alipromotions.bcn</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=clicked dm=sent email=sent wa=no-composer</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L160</t>
+          <t>L177</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hybrd Academy</t>
+          <t>Academiamariopadilla</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>34659425174</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>34692382544</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>mario@academiamariopadilla.com</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>COMPLETE: follow=None dm=None email=None wa=no-composer</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L177</t>
+          <t>L183</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Academiamariopadilla</t>
+          <t>Shudokan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>34661571463</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>34659425174</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>mario@academiamariopadilla.com</t>
+          <t>info@shudokan.es</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>@ancora_themes</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@shudokan.roje</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L183</t>
+          <t>L185</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shudokan</t>
+          <t>Clubtakeda</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>34620517614</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>34661571463</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>info@shudokan.es</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>@shudokan.roje</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
-        </is>
-      </c>
+          <t>info.clubtakeda@gmail.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L185</t>
+          <t>L187</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clubtakeda</t>
+          <t>Crossboxgym</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>34649316067</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>34620517614</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>info.clubtakeda@gmail.com</t>
+          <t>crossboxgym@gmail.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L187</t>
+          <t>L188</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Crossboxgym</t>
+          <t>Crossboxing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>34620067869</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>34649316067</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>crossboxgym@gmail.com</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>info@crossboxing.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>@crossboxing.es</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L188</t>
+          <t>L252</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Crossboxing</t>
+          <t>Dgmma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>491773216092</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>34620067869</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>info@crossboxing.com</t>
+          <t>hello@dgmma.de</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>@crossboxing.es</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@dragongatemma</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L252</t>
+          <t>L254</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dgmma</t>
+          <t>Elysium Mma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>4917643525310</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>491773216092</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>hello@dgmma.de</t>
+          <t>info@elysium-mma.de</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>@dragongatemma</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@elysium_mma_munich</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L254</t>
+          <t>L255</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Elysium Mma</t>
+          <t>Tripleonegym</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>491734496111</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>4917643525310</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>info@elysium-mma.de</t>
+          <t>info@tripleonegym.de</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>@elysium_mma_munich</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@tripleonegym</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L255</t>
+          <t>L267</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tripleonegym</t>
+          <t>Kickboxingvomero</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>39335344423</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>491734496111</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>info@tripleonegym.de</t>
+          <t>kickboxingvomero@gmail.com</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@tripleonegym</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@kickboxingvomero</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L267</t>
+          <t>L269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kickboxingvomero</t>
+          <t>Mgmboxeisland</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>393896699615</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>39335344423</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>kickboxingvomero@gmail.com</t>
+          <t>info@101sport.net</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>@kickboxingvomero</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@MGM_MIlano</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L269</t>
+          <t>L287</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mgmboxeisland</t>
+          <t>Bokshuis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>31642692144</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>393896699615</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>info@101sport.net</t>
+          <t>info@bokshuis.nl</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>@MGM_MIlano</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@bokshuis</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L287</t>
+          <t>L347</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bokshuis</t>
+          <t>Tkoboxingclub</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>447538916121</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>31642692144</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>info@bokshuis.nl</t>
+          <t>team@tkoboxingclub.co.uk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>@bokshuis</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@tkoboxingclub</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L347</t>
+          <t>L350</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tkoboxingclub</t>
+          <t>Kenglengmuaythai</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>07496652323</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>447538916121</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>team@tkoboxingclub.co.uk</t>
+          <t>kenglengmuaythai@gmail.com</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>@tkoboxingclub</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+          <t>@kengleng.muaythai</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L350</t>
+          <t>L354</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kenglengmuaythai</t>
+          <t>Adrenalinemt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>447920887358</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>07496652323</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>kenglengmuaythai@gmail.com</t>
+          <t>admin@adrenalinemt.uk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>@kengleng.muaythai</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>L354</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Adrenalinemt</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+          <t>@adrenaline_muay_thai</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Lead ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Old status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L039</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kick &amp; Punch Milano DownTown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>393914124452</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + WhatsApp sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L044</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sokudo Gym Hoorn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31229215582</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + WhatsApp sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L046</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gracie Barra Braga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>351927773854</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG DM sent + WhatsApp sent (follow btn n</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L048</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kickboxing Madrid</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>34685660511</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent +</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L049</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CrossBox Gym</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>34649316067</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent +</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L050</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DM Fight</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>34613268619</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent +</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L051</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Draco Fight Club</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>34667720380</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent +</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L055</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Slava Legacy Gym</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34674387362</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (email n/a) + IG follow pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L056</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wuxing Madrid</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>34643340522</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG follow p</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L059</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mugendo Martial Arts Eixample</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>34646739122</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (Mugendo Eixample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L062</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HardiFit</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>34662494150</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L065</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fight Culture</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>351963631744</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L066</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Porradaria Ate'o Talho</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>351913200732</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (Porradaria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L068</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lucero Muay Thai Madrid</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>34633215305</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (Lucero)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L072</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Muay Thai Kassel</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4956181696280</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L090</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Akhi Sport Gym</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>31650514751</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L093</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Amsterdam Training Center</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>31627006861</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L094</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Freddy's Kickboxing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>31613701879</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L096</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sukhothai Academy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4978219228338</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L097</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KOI Gym Frankfurt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>491743505229</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L098</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Champs Kickboxing Berlin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4930233208320</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L106</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Boxing Trainer London</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>447790210031</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>447920887358</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>admin@adrenalinemt.uk</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>@adrenaline_muay_thai</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>COMPLETE: email sent</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L130</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PT do Bairro</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>351931468801</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L134</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Studio Absoluto JJ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>351934624841</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L135</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AMDKP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>351911165714</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L138</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Spirit Academy 74</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>41796061009</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L139</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Beat 35 Studio</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>33672587591</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L141</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Le Hook Vieux Lille</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>33766685436</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L142</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bennies Boxing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>447961557534</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L163</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Armazém Jiu-Jitsu</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>351925896645</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L164</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fred Motta Muay Thai</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>351968718777</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L165</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Z Fortes Muay Thai</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>351965577023</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed</t>
         </is>
       </c>
     </row>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOT LEAD (negotiating): picked MMA shorts + MMA tights + JJ gi, asked details. Sent full specs + quantity question 2026-10-15. Awaiting quantities for exact quote + mockup.</t>
+          <t>HOT LEAD (negotiating): picked MMA shorts + MMA tights + JJ gi; 16 Oct 1:16 AM asked 'Do you have any photo to show some examples?' - DRAFT with AI product photos ready, awaiting user send approval</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RE-SENT first template via NEW WA number 2026-10-15</t>
+          <t>Follow-up sent 2026-10-16 (reference old pads+gloves chat + free logo branding value). Awaiting reply.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
+          <t>COMPLETE: IG followed + IG DM sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent (follow btn n/a - already following)</t>
+          <t>COMPLETE: IG DM sent (follow btn n/a - already following) | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent + email sent (info@koteam.pt)</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent (info@koteam.pt) | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
+          <t>COMPLETE: IG followed + IG DM sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>RE-SENT first template via NEW WA number 2026-10-15</t>
+          <t>Follow-up sent 2026-10-16 (fight-team package angle: 2-3 items + exact pricing offer). Awaiting reply.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RE-SENT first template via NEW WA number 2026-10-15</t>
+          <t>Follow-up sent 2026-10-16 (ultra-short + 'reply yes' micro-commitment). Awaiting reply.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOT LEAD (negotiating): picked MMA shorts + MMA tights + JJ gi; 16 Oct 1:16 AM asked 'Do you have any photo to show some examples?' - DRAFT with AI product photos ready, awaiting user send approval</t>
+          <t>HOT LEAD (payment stage): asked Dirham or Euro. Answered: Euro pricing, he pays Dirham via Western Union, we receive local currency. Awaiting his confirmation + logo. Sample EUR 77.40.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1535,7 +1535,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent [IG handle was junk - removed]</t>
+          <t>COMPLETE: email sent [IG handle was junk - removed] | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1615,7 +1615,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1653,7 +1653,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM + WA + email sent</t>
+          <t>COMPLETE: IG followed + IG DM + WA + email sent | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM + email + WA sent (email re-confirmed v4)</t>
+          <t>COMPLETE: IG followed + IG DM + email + WA sent (email re-confirmed v4) | COMPLETE: email sent (Day 6, 2026-10-19)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>COMPLETE: already-following + IG DM + email + WA sent (email re-confirmed v4)</t>
+          <t>COMPLETE: already-following + IG DM + email + WA sent (email re-confirmed v4) | COMPLETE: email sent (Day 6, 2026-10-19)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Follow-up sent 2026-10-16 (reference old pads+gloves chat + free logo branding value). Awaiting reply.</t>
+          <t xml:space="preserve"> | Follow-up 2 sent 2026-10-17 (training vs competition question). | COMPLETE: email sent (Day 6, 2026-10-19) | WA sent (Day 6) | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=ok dm=sent email=sent wa={"ok":true,"last":["Hola Ippon Gear España! \n\n\n\nHola Ippon G"]}</t>
+          <t>COMPLETE: follow=ok dm=sent email=sent wa={"ok":true,"last":["Hola Ippon Gear España! \n\n\n\nHola Ippon G"]} | COMPLETE: email sent (Day 6, 2026-10-19) | WA sent (Day 6) | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: IG followed + IG DM sent | WA sent (Day 5 wave) | COMPLETE: email sent (Day 6, 2026-10-19)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -751,7 +751,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola Al-Andalus Judo Sevilla! \n\n\n\nwe mak"]}</t>
+          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola Al-Andalus Judo Sevilla! \n\n\n\nwe mak"]} | COMPLETE: email sent (Day 6, 2026-10-19) | WA sent (Day 6)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent (follow btn n/a - already following) | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: IG DM sent (follow btn n/a - already following) | WA sent (Day 5 wave) | COMPLETE: email sent (Day 6, 2026-10-19)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -827,7 +827,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Judo Kitaro! \n\n\n\nwe make custom mar"]}</t>
+          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Judo Kitaro! \n\n\n\nwe make custom mar"]} | WA sent (Day 6)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=no-btn dm=sent email=sent wa={"ok":true,"last":["Hola Brazilian Fight Lisboa! \n\n\n\nwe make"]}</t>
+          <t xml:space="preserve"> | REPLIED + PT follow-up sent 2026-10-20 (quantity question, factory prices, academy branding). | IG not found</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Gracie Lisboa! \n\n\n\nmartial arts &amp; s"]}</t>
+          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Gracie Lisboa! \n\n\n\nmartial arts &amp; s"]} | WA sent (Day 6)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola APKO Okinawa Karate! \n\n\n\nmartial ar"]}</t>
+          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola APKO Okinawa Karate! \n\n\n\nmartial ar"]} | COMPLETE: email sent (Day 6, 2026-10-19) | WA sent (Day 6)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34621413059</t>
+          <t>+34621413059</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=ok dm=sent email=None wa={"ok":true,"last":["Hello FullGym 24h Vilafranca! \n\n\n\nwe pro"]}</t>
+          <t>COMPLETE: follow=ok dm=sent email=None wa={"ok":true,"last":["Hello FullGym 24h Vilafranca! \n\n\n\nwe pro"]} | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33664204654</t>
+          <t>+33664204654</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Follow-up sent 2026-10-16 (fight-team package angle: 2-3 items + exact pricing offer). Awaiting reply.</t>
+          <t xml:space="preserve"> | Follow-up 2 sent 2026-10-17 (default 10x package quote offer). | COMPLETE: email sent (Day 6, 2026-10-19) | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>393514088140</t>
+          <t>+393514088140</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Follow-up sent 2026-10-16 (ultra-short + 'reply yes' micro-commitment). Awaiting reply.</t>
+          <t xml:space="preserve"> | Follow-up 2 sent 2026-10-17 (EUR 19.50 anchor + no-minimum trial offer). | COMPLETE: email sent (Day 6, 2026-10-19) | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>351916033601</t>
+          <t>+351916033601</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOT LEAD (payment stage): asked Dirham or Euro. Answered: Euro pricing, he pays Dirham via Western Union, we receive local currency. Awaiting his confirmation + logo. Sample EUR 77.40.</t>
+          <t xml:space="preserve"> | Follow-up 2 sent 2026-10-17 (mockup-first offer, EUR 77.40 all-in). Awaiting logo. | COMPLETE: email sent (Day 6, 2026-10-19) | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33783401554</t>
+          <t>+33783401554</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>353873256588</t>
+          <t>+353873256588</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=no-btn dm=sent email=recipient-not-registered wa={"ok":true,"last":["Hello Angels Boxing! \n\n\n\nmartial arts &amp; "]}</t>
+          <t>COMPLETE: follow=no-btn dm=sent email=recipient-not-registered wa={"ok":true,"last":["Hello Angels Boxing! \n\n\n\nmartial arts &amp; "]} | EMAIL FAILED (Day 6) | IG follow=no-btn dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>491737513627</t>
+          <t>+491737513627</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=clicked dm=sent email=None wa=no-composer</t>
+          <t>COMPLETE: follow=clicked dm=sent email=None wa=no-composer | IG follow=ok dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>491708890687</t>
+          <t>+491708890687</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1379,7 +1379,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa=no-composer</t>
+          <t>COMPLETE: follow=None dm=None email=sent wa=no-composer | COMPLETE: email sent (Day 6, 2026-10-19)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L158</t>
+          <t>L159</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Crossbox Gym</t>
+          <t>Ali Promotions BCN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>34649316067</t>
+          <t>+34687075304</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>crossboxgym@protonmail.com</t>
+          <t>alipromotions.bcn@gmail.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>@crossboxgym</t>
+          <t>@alipromotions.bcn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=no-btn dm=sent email=sent wa=no-composer</t>
+          <t>COMPLETE: follow=clicked dm=sent email=sent wa=no-composer | COMPLETE: email sent (Day 6, 2026-10-19) | IG follow=ok dm=sent (Day 6)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1433,12 +1433,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L159</t>
+          <t>L160</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ali Promotions BCN</t>
+          <t>Hybrd Academy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1448,22 +1448,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34687075304</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>alipromotions.bcn@gmail.com</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>@alipromotions.bcn</t>
-        </is>
-      </c>
+          <t>+34692382544</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=clicked dm=sent email=sent wa=no-composer</t>
+          <t>COMPLETE: follow=None dm=None email=None wa=no-composer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1475,12 +1467,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L160</t>
+          <t>L177</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hybrd Academy</t>
+          <t>Academiamariopadilla</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1490,31 +1482,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34692382544</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>34659425174</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>mario@academiamariopadilla.com</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=None wa=no-composer</t>
+          <t>COMPLETE: email sent [IG handle was junk - removed] | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Day 3 hunt batch</t>
+          <t>Day 4 night batch</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L177</t>
+          <t>L183</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Academiamariopadilla</t>
+          <t>Shudokan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1524,18 +1520,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34659425174</t>
+          <t>34661571463</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mario@academiamariopadilla.com</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>info@shudokan.es</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>@shudokan.roje</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent [IG handle was junk - removed] | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L183</t>
+          <t>L185</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shudokan</t>
+          <t>Clubtakeda</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1562,22 +1562,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>34661571463</t>
+          <t>34620517614</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>info@shudokan.es</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>@shudokan.roje</t>
-        </is>
-      </c>
+          <t>info.clubtakeda@gmail.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: email sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1589,12 +1585,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L185</t>
+          <t>L187</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clubtakeda</t>
+          <t>Crossboxgym</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1604,12 +1600,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>34620517614</t>
+          <t>34649316067</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>info.clubtakeda@gmail.com</t>
+          <t>crossboxgym@gmail.com</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1627,12 +1623,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L187</t>
+          <t>L188</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Crossboxgym</t>
+          <t>Crossboxing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1642,18 +1638,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>34649316067</t>
+          <t>34620067869</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>crossboxgym@gmail.com</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>info@crossboxing.com</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>@crossboxing.es</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found | WA sent (Day 5 wave) | IG not found</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1665,37 +1665,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L188</t>
+          <t>L252</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Crossboxing</t>
+          <t>Dgmma</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>34620067869</t>
+          <t>491773216092</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>info@crossboxing.com</t>
+          <t>hello@dgmma.de</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>@crossboxing.es</t>
+          <t>@dragongatemma</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L252</t>
+          <t>L254</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dgmma</t>
+          <t>Elysium Mma</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1722,22 +1722,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>491773216092</t>
+          <t>+4917643525310</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>hello@dgmma.de</t>
+          <t>info@elysium-mma.de</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@dragongatemma</t>
+          <t>@elysium_mma_munich</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1749,12 +1749,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L254</t>
+          <t>L255</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elysium Mma</t>
+          <t>Tripleonegym</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1764,22 +1764,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4917643525310</t>
+          <t>+491734496111</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>info@elysium-mma.de</t>
+          <t>info@tripleonegym.de</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>@elysium_mma_munich</t>
+          <t>@tripleonegym</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA FAILED (Day 7): no-composer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1791,37 +1791,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L255</t>
+          <t>L267</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tripleonegym</t>
+          <t>Kickboxingvomero</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>491734496111</t>
+          <t>+39335344423</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>info@tripleonegym.de</t>
+          <t>kickboxingvomero@gmail.com</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>@tripleonegym</t>
+          <t>@kickboxingvomero</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1833,12 +1833,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L267</t>
+          <t>L269</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kickboxingvomero</t>
+          <t>Mgmboxeisland</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1848,22 +1848,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>39335344423</t>
+          <t>+393896699615</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>kickboxingvomero@gmail.com</t>
+          <t>info@101sport.net</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>@kickboxingvomero</t>
+          <t>@MGM_MIlano</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1875,37 +1875,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L269</t>
+          <t>L287</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mgmboxeisland</t>
+          <t>Bokshuis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>393896699615</t>
+          <t>+31642692144</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>info@101sport.net</t>
+          <t>info@bokshuis.nl</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>@MGM_MIlano</t>
+          <t>@bokshuis</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1917,37 +1917,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L287</t>
+          <t>L347</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bokshuis</t>
+          <t>Tkoboxingclub</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31642692144</t>
+          <t>+447538916121</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>info@bokshuis.nl</t>
+          <t>team@tkoboxingclub.co.uk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>@bokshuis</t>
+          <t>@tkoboxingclub</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1959,12 +1959,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L347</t>
+          <t>L350</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tkoboxingclub</t>
+          <t>Kenglengmuaythai</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1974,17 +1974,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>447538916121</t>
+          <t>+07496652323</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>team@tkoboxingclub.co.uk</t>
+          <t>kenglengmuaythai@gmail.com</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>@tkoboxingclub</t>
+          <t>@kengleng.muaythai</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2001,12 +2001,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L350</t>
+          <t>L354</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kenglengmuaythai</t>
+          <t>Adrenalinemt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2016,22 +2016,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>07496652323</t>
+          <t>+447920887358</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>kenglengmuaythai@gmail.com</t>
+          <t>admin@adrenalinemt.uk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>@kengleng.muaythai</t>
+          <t>@adrenaline_muay_thai</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent | WA sent (Day 8) - verified transcript</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2043,42 +2043,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L354</t>
+          <t>L581</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Adrenalinemt</t>
+          <t>Pugilistica Elite Milano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>447920887358</t>
+          <t>+393514002388</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>admin@adrenalinemt.uk</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>@adrenaline_muay_thai</t>
-        </is>
-      </c>
+          <t>info@pugilisticaelite.com</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
+          <t>COMPLETE: email sent (Day 7 test-send, 2026-10-19) | WA sent (Day 7) - verified transcript</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Day 4 night batch</t>
+          <t>Hunted 2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>L585</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fight District Amsterdam</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>+31629144029</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>hello@fightdistrict.nl</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HUNTED (Day 6 pre-dawn, schema repaired Day 7) | COMPLETE: email sent (Day 7, 2026-10-19) | WA sent (Day 7) - verified transcript</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Hunted 2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>L595</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Combatgym.ch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>+41792740620</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HUNTED (Day 6 pre-dawn, schema repaired Day 7) | WA sent (Day 7) - verified transcript</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Hunted 2026-10-19 1AM</t>
         </is>
       </c>
     </row>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2150,6 +2150,4928 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>L793</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wutian BJJ &amp; Kickboxing in Isle of Dogs</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>+442081583986</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>info@wutianmartialart.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>L794</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Xen-Do Martial Arts</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>+442074873807</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>L795</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>London Fight Factory</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>+447944574046</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>info@londonfightfactory.com</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>L796</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fightzone London</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>+442077293907</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>fightzonelondon@gmail.com</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>L797</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AVALON Mixed Martial Arts Academy - MMA, BJJ, Wing Chun</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>+447976855259</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 9) - verified transcript</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>L798</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ryu-Kai Martial Arts</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>+442033369040</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>admin@ryu-kai.com</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>L799</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>London Fight Academy</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>+442088232323</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>info@londonfightacademy.com</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>L800</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Elite Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>+447516916432</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>elite-maa@outlook.com</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>L801</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Legacy Martial Arts London</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>+447857948554</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>info@legacymartialartslondon.co.uk</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>L802</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tokei Martial Arts and Fitness Centre</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>+442074035979</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>L803</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KO Combat Academy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>+442072659693</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>info@kocombatacademy.com</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>L804</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The Martial Arts Place</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>+442072540332</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>L805</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Islington Martial Arts</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>+447503554872</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>L806</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>The London Jiu Jitsu Centre</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>+447591492052</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>admin@londonjiujitsucentre.com</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L807</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Xen-Do Martial Arts</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>+442078134293</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>L808</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Fight City Gym - Moorgate</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>+442070436032</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L809</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>The Budokwai</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>+442073701000</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>office@budokwai.co.uk</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L810</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Bruce Lee's Jeet Kune Do with JKD London (Sifu Lak Loi)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>+447438308367</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>L811</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Koryo Taekwondo Academy London</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>+447910061481</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L813</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>London Grapple</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>+442037717955</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>info@londongrapple.co.uk</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L814</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>The Gentle Arts School</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>+447360334349</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>rayder@thegentleartschool.co.uk</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L815</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Leo Wing Chun Chinese Kung Fu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>+447887427765</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>info@chinesekungfu.co.uk</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L816</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meiji Martial Arts (Temple Fortune Dojo) / Kickboxing / Jiu </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>+442075865880</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L817</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Shorinji Kempo - London Self Defence Martial Art</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>+447713482314</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>L818</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Diesel Gym London</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>+447765243012</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>L819</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>London Combat MMA Academy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>+447930824601</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>londoncombat@gmail.com</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>L822</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TEAM SHARK CLAPHAM JUNCTION Martial Arts Academy. Muay Thai.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>+447949029157</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>L823</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Xen-Do Martial Arts</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>+442077230206</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>L824</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Daigaku Karate Kai (University of Westminster Karate Club)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>+447976411901</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>info@goju-karate.co.uk</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L825</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sanda Kickboxing Academy London</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>+447920056974</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>info@sandakickboxingacademy.co.uk</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L826</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Qwan Ki Do &amp; Tai Chi - Martial Arts Club</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>+447737825087</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>info@qwankido.co.uk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L828</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Karoon Taekwondo Academy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>+447903570600</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L829</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>STARTA Brazilian Jiu-Jitsu London</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>+447564434982</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>info@mysite.com</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L830</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>London Taekwondo Academy Ltd</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>+447857967855</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L831</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>New Cross Martial Arts</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>+447821679058</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>neil@newcrossmartialarts.com</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>L832</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gurumu Taekwondo - Olympic Martial Arts</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>+447931709140</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>L833</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Bromley Martial Arts Academy (Black Belt School)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>+447720218455</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>L834</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Shaolin Temple UK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>+442076878333</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>info@shaolintempleuk.org</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>L836</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SBL London Academy</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>+447723009164</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L837</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>East London Shorinji Kempo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>+442081232824</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L838</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Boado Academy of Martial Arts BAMA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>+447751813956</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>chrisboado@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>L839</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Peak Performance Taekwondo Academy - Olympic Martial arts ce</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>+447961534525</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>info@peakperformancetkd.co.uk</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L840</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jeffrey Alexander School of Martial Arts (JASMA)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>+447909914567</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L841</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Westminster Shotokan Karate Club</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>+447956593184</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>L842</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sanjuro Martial Arts</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>+447779249469</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>anita@sanjurotrainingsystems.com</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L843</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Docklands Kyokushinkai Karate Club</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>+447801406639</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>kem.resh@outlook.com</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>L844</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MD Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>+447960599125</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>sifumarcdavis@gmail.com</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L845</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tactical Thai Sword London</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>+447837643316</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>L846</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Stoa Grappling</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>+447540841820</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>info@stoagrappling.com</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L847</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Roger Gracie Brazilian Jiu Jitsu Academy HQ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>+442087410231</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>academy@rogergracie.com</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>L848</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Roger Gracie Euston</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>+447365331358</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>contact@rogergracieeuston.com</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>L849</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Carlson Gracie London</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>+447518111170</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>info@bjjlondon.com</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>L850</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BALANCE BRAZILIAN JIU JITSU ACADEMY</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>+447360542667</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>info@balancebjj.co.uk</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L851</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Alliance Jiu Jitsu London</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>+442080791044</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>hello@alliancejjlondon.com</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>L852</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Kodokan Academy of Brazilian Jiu Jitsu - BJJ School London</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>+447834230066</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>sensei@thekodokan.com</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>L853</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BJJ ART UK - Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>+447565132401</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>bjj4all.ltd@gmail.com</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>L854</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Putney Jiu Jitsu - 5* BJJ Gym in South West London</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>+447716222602</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>info@putneybjj.com</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>L855</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BJJ Dojo</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>+447841764210</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>info@bjjhouse.co.uk</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>L856</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Luciano Cristovam BJJ Academy</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>+447498471113</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>L857</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Gracie Barra Oval</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>+447734463932</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>info@graciebarraoval.com</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>L859</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ARMA Jiu Jitsu Club</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>+442081290847</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>info@armabjj.com</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>L860</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cantagalo JiuJitsu London</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>+447902491656</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>cantagalojiujitsulondon@gmail.com</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L861</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Grapple Zone Brazilian Jiu Jitsu, Waterloo</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>+447496636266</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>admin@grapplezone.co.uk</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L862</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>10th Planet Jiu Jitsu London</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>+447984973337</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>L863</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Wave Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>+442080128355</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>info@wavebjj.co</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L865</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PURE JIUJITSU</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>+447521420733</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>info@purejiujitsu.com</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L866</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>London Ju Jitsu - Elephant and Castle</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>+447903190978</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>info@londonjujitsu.com</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L867</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Manchester Karate - Missing Link in Manchester</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>+447539946777</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>manchester@missinglink-martialarts.uk</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L869</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fighting Fit Manchester</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>+447385187483</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>gym@fightingfitmanchester.co.uk</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L870</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shaolin Kung Fu - Gao Can Mun Nam Pai Chuan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>+447887776132</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>manchestershaolinnpc@gmail.com</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L871</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Didsbury Black Belt Academy</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>+441614457733</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>L872</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Union Academy Manchester - BJJ and Kickboxing Academy</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>+442088168382</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L873</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Solid MMA Manchester</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>+447543619474</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>info@solidmmamanchester.co.uk</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L874</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>K.M.M.A. Freestyle Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>+447961914054</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>kmmafreestyle.info@gmail.com</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L875</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Predators MMA and BJJ Academy Manchester</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>+447897313488</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>predatorsmmagym@gmail.com</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>L876</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ip Man Wing Chun Kung Fu Manchester</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>+447593913883</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>L877</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Advanced Basics MMA Gym Manchester</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>+447856969170</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>L878</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Henshall Brazilian jiu jitsu</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>+447475938425</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>L879</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Mo's Martial Arts Centre</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>+447811575614</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>L880</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>North Manchester Family Martial Arts Centre (Prestwich)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>+447811006469</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>fmacnorthmanchester@gmail.com</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>L881</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>STRETFORD MARTIAL ARTS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>+447591214756</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>stretfordmartialarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>L882</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Krav Maga Manchester FEKM</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>+447519038169</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>L883</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Franks Team Sports Club - MMA - BOXING - BJJ - Fitness</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>+447713499484</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>L885</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Wayfarer Academy®</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>+447700148142</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>L886</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mantkd Taekwondo Academy</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>+447946650820</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>info@mantkd.co.uk</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>L887</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Salford Mixed Martial Arts</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>+441617430028</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>L888</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Chi mo martial art Centre</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>+447847888828</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>L889</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AK Academy of Martial Arts</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>+447932592556</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>L891</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Master A Muay Thai</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>+447791040637</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>L892</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Roger Gracie BJJ Academy Salford in Manchester</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>+447506746662</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>info@rgasalford.co.uk</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>L893</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AP TAEKWONDO ACADEMY - Gorton</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>+447743991146</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>L895</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MMU Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>+441612476447</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>L896</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Bee-Safe Manchester</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>+447525441949</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>beesafemanchester@gmail.com</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>L897</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Red Tiger Karate - Old Trafford</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>+447825446825</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>info@redtigerkarateclub.co.uk</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>L898</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Temple Kickboxing Didsbury</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>+447838355221</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>L899</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Stealth BJJ - Manchester Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>+447903644928</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>info@stealthbjj.com</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>L901</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>J M Taekwondo</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>+447738497319</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>matt@pixelspread.com</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>L902</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sharman Taekwon-Do</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>+447511767186</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>haohao.jiang+designer@strikingly.com</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>L904</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Tai Chi Kung Fu Centre</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>+447765922725</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>tckfc.info@gmail.com</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>L905</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Lishi Tai Chi Classes in Manchester</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>+447761882289</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>L906</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>British Taekwondo</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>+441616975330</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>membership.services@britishtaekwondo.org</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>L907</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Salford Martial Arts</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>+447799424337</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>L908</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Jason Baird's Black Belt Academy</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>+447949066244</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>L909</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Trident Taekwon-Do Academy</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>+447974649015</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>hello@tridenttkdmanchester.co.uk</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>L910</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Openshaw Shukokai Karate Club. East Manchester Leisure Centr</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>+447799827017</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>L911</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Cobra Martial Arts Association</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>+447909673894</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>cmaauk@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>L912</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Family Martial Arts Centres - Urmston</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>+447801498677</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>urmstonfmac@outlook.com</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>L913</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Valour JiuJitsu Manchester</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>+447843304308</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>valourbjj@proton.me</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>L914</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Family Martial Arts Centres Swinton</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>+441617284449</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>info@familymartialartscentres.com</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>L916</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Athena Muay Thai</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>+447930511659</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>athenamtb@gmail.com</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>L917</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Gym 72</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>+441612360686</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>info@gym72.co.uk</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>L918</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Fight Factory Manchester</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>+447746661931</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>your@email.com</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>L919</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>GZ Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>+447776437440</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>L920</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Moss Side Boxing &amp; Athletics Association</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>+441612278708</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>L922</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Arnies Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>+447951246860</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>L923</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Fit2Fight</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>+443300888974</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>info@fit2fightgym.co.uk</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>L924</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Collyhurst and Moston Lads Club</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>+441616835046</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>L925</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Collyhurst and Moston ABC</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>+447832983843</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>L926</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Paulino’s Boxing</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>+447510947761</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>L927</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FRANK'S</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>+447467435330</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>frank@frankwellness.co.uk</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>L928</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Moss Side Fire Station Boxing Club</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>+441616085215</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>mosssidefirestationboxingclub@gmail.com</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>L929</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>OnPoint Boxing Club</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>+447944838529</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>L930</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Oliver's Gym</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>+447757623229</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>L932</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Kickboxing</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>+447774723839</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>chris.nwckb@gmail.com</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>L933</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Fighting Fit Elite Performance Centre</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>+447951219442</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>L934</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Jimmy Egan’s Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>+447886035030</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>jimmyegansboxingacademycic@outlook.com</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>L935</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>M27 Boxing and Fitness</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>+441615665798</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>L936</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Barton Athletic Club</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>+441617078124</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>L937</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Urban Reform</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>+447854868113</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>urbanreformfit@gmail.com</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>L938</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>The Yard Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>+447562648802</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>L939</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Manchester Top Team</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>+447863877959</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>contact@manchestertopteam.com</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>L940</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Salford City Boxing Academy (Dorvy)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>+447748567595</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>L941</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>The Olympus Projects</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>+441615472679</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>train@theolympusprojects.com</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>L942</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Health Lab</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>+447554299598</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>L944</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Salford Striking Academy</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>+447890869960</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>L945</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Urmston Boxing Club</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>+447759383081</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>L946</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Delaneys gym</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>+447927127256</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>L947</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ROC BoxFit</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>+447833257747</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>roconnor1978</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | IG follow=ok dm=sent (Day 9)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>L948</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Manchester Fighters Academy</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>+447770583190</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>L949</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Wickstead Muay Thai</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>+447500584846</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>L951</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Hive Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>+447476927426</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>L952</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3rothers Gym- Mixed Martial Arts and Fitness Gym</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>+447496555708</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>3rothersgym@gmail.com</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>L953</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ONE MMA Academy Manchester</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>+447398896732</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>L954</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TKO Gym Manchester</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>+447448573150</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>support@webador.com</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>L955</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Viva MMA BJJ &amp; Kickboxing</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>+441613123100</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>L956</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Academia BJJ Lifestyle UK</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>+447549966379</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>L957</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Phoenix Muay Thai Boxing</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>+447973697683</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>train@phoenixmuaythai.co.uk</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>L958</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Factory BJJ - Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>+441613008795</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>admin@factorybjj.com</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>L959</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>12 Gauge MMA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>+441614949191</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>info@12gaugemma.com</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>L960</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Adrenaline Combatives</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>+447555486603</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>L961</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Black Tiger Martial Arts</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>+447760543735</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>blacktigerkarate@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>L962</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Manchester Martial Arts &amp; Gym Supply</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>+441616378110</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>L963</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Matratz BJJ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>+447715549105</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ashley@matratzbjj.com</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found | WA sent (Day 5 wave) | IG not found</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found | WA sent (Day 5 wave) | IG not found | EMAIL FAILED (bounce confirmed 2026-10-24)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2823,7 +2823,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Daily 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Daily 2026-10-23) | EMAIL FAILED (bounce confirmed 2026-10-24)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -5773,7 +5773,7 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (sprint Day 1, 2026-10-22)</t>
+          <t xml:space="preserve">HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (sprint Day 1, 2026-10-22) | EMAIL FAILED (bounce confirmed 2026-10-24) | EXCLUDED (scrape contamination: email cell is not a valid address) </t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -9713,7 +9713,7 @@
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: garbage scraped email</t>
+          <t xml:space="preserve">HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: garbage scraped email | EXCLUDED (scrape contamination: email cell is not a valid address) </t>
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
@@ -15277,7 +15277,7 @@
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: image-filename scraped as email</t>
+          <t xml:space="preserve">HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: image-filename scraped as email | EXCLUDED (scrape contamination: email cell is not a valid address) </t>
         </is>
       </c>
       <c r="H449" t="inlineStr"/>
@@ -15345,7 +15345,7 @@
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: image-filename scraped as email</t>
+          <t xml:space="preserve">HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: image-filename scraped as email | EXCLUDED (scrape contamination: email cell is not a valid address) </t>
         </is>
       </c>
       <c r="H451" t="inlineStr"/>
@@ -15413,7 +15413,7 @@
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: image-filename scraped as email</t>
+          <t xml:space="preserve">HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED: image-filename scraped as email | EXCLUDED (scrape contamination: email cell is not a valid address) </t>
         </is>
       </c>
       <c r="H453" t="inlineStr"/>
@@ -16325,7 +16325,7 @@
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t xml:space="preserve">HUNTED (gmaps 2PM 2026-10-23) | EXCLUDED (scrape contamination: email cell is not a valid address) </t>
         </is>
       </c>
       <c r="H481" t="inlineStr"/>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H877"/>
+  <dimension ref="A1:H1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -29014,6 +29014,5782 @@
       </c>
       <c r="H877" t="inlineStr"/>
     </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>L1732</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>STAT Campo de Ourique</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>+351938867035</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>L1733</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>YMAA Portugal - Lisboa</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>+351928038296</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>info.aamyp@gmail.com</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>L1734</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Elite Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>+351913739070</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>L1735</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Alpha Combat Premium Martial Arts</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>+351933881631</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>info@alpha-combat.com</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>L1736</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Alliance Jiu Jitsu - Parque das Nações, Lisboa</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>+351924851474</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>L1738</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Jisei Dojo</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>+351211608214</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>L1739</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Sakura Training Center</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>+351916571740</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>sakuraportugal@gmail.com</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>L1740</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>VMA São Domingos de Benfica</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>+351932669717</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>sdbenfica@vma.com.pt, alfragide@vma.com.pt, email@dominio.pt</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>L1741</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Brasa Clube de Jiu Jitsu Lisboa</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>+351927077525</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>L1743</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Netto bjj - Pantera House</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>+351929247339</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>user@domain.com, usuario@dominio.com</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>L1744</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>FCF Legacy Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>+351915507460</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>L1745</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>STAT Restelo</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>+351938867033</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>L1746</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Sampaio Brazilian Jiu-Jitsu - Lisboa</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>+351912214115</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>sampaiobjj_fcs.loures</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>L1747</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Systema Moncada - Russian Martial Art</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>+351969690139</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>L1748</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Academia Mestre Chung</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>+351913978975</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>L1749</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>FEU BJJ Lisboa</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>+351960235163</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>L1750</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>PROJ3K7 ACADEMY</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>+351914344956</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com, f36cc48fb72b4d298c835f2793cf3b84@sentry-next.wixpress.com, dd0a55ccb8124b9c9d938e3acf41f8aa@sentry.wixpress.com, c183baa23371454f99f417f6616b724d@sentry.wixpress.com, 8c4075d5481d476e945486754f783364@sentry.io, 88170cb0c9d64f94b5821ca7fd2d55a4@sentry-next.wixpress.com, 463991d7bca24f02a0baf16f9e6eda73@sentry.wixpress.com, 1eeb89147c984dc6bc3ffafd9e6cd089@sentry.wixpress.com, 9a65e97ebe8141fca0c4fd686f70996b@sentry.wixpress.com, ed436f5053144538958ad06a5005e99a@sentry.wixpress.com, 460ff4620fa44cba8df530afde949785@sentry.wixpress.com, 79baaa8e09c746d2b7401643b99792e0@sentry.wixpress.com, 2062d0a4929b45348643784b5cb39c36@sentry.wixpress.com, 8eb368c655b84e029ed79ad7a5c1718e@sentry.wixpress.com, 78f7996315bc402f9dcb8a2f974b82d1@sentry.wixpress.com, 271e9fa3230b4eec94b02bf95780f5f2@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>L1752</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Budokai de Lisboa</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>+351969006742</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr"/>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>L1753</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>INATEL Artes Marciais Taekwondo</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>+351966327529</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>taekwondo.shimjun@gmail.com</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>L1754</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Karate Goju-Ryu Portugal</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>+351936194553</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>L1755</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Escola de Lutas Olímpicas Carlos Goshi Team</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>+351962819832</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>L1756</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Academia Luso Warrior</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>+351966036606</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>L1757</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>ANKS - Associação Nacional de Karate Shotokan</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>+351934204868</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>info@anks.pt, u003einfo@anks.pt</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>L1758</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>BROSS Martial Arts</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>+351931740635</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>L1759</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Krav Magá Mestre Kobi - Portugal</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>+351910529826</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>kravmaga@kravmaga.com.br</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>L1760</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Reborn Fight Team</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>+351937655508</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>hussainmazhar558@gmail.com, info@tehreembco.com</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>L1761</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>AGOKAP - Associação Goju-Ryu Karate-Do de Portugal</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>+351929009883</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>L1762</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>STHENOS FIGHT LUMIAR - Calistenia Portugal</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>+351927008654</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>L1763</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>NARÉ Fighters</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>+351917165143</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>L1764</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>VITORIA - Nobre Arte</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>+351213850110</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>info@vitoria.club</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>L1765</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Pachi Tanglang Lisboa</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>+351926860098</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>L1766</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Rounds Academy</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>+351211303924</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>rounds.academy@gmail.com</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>L1767</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Karate Sporting - Lisboa</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>+351918798854</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>info@ippon.pt</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>L1768</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Isshin Dojo</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>+351918228949</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>isshindojo.lx@gmail.com</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>L1769</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Like Water</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>+351927750376</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>L1770</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Pa-Kua Encarnação</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>+351967898754</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>L1771</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Endless Team Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>+351912540271</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com, 8c4075d5481d476e945486754f783364@sentry.io, dd0a55ccb8124b9c9d938e3acf41f8aa@sentry.wixpress.com, c183baa23371454f99f417f6616b724d@sentry.wixpress.com, 9a65e97ebe8141fca0c4fd686f70996b@sentry.wixpress.com, 8eb368c655b84e029ed79ad7a5c1718e@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>L1772</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Jiu Jitsu Pura Conexão</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>+351915946785</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>L1773</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Gracie Barra Parque Das Nações</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>+351218081934</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>L1774</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Mais Taekwondo</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>+351965542941</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>geral@amtportugal.com</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>L1776</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Arena Lisboa</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>+351914310656</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>L1777</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Gold Glove - Boxe &amp; Kickboxing, Alvalade, Lisboa</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>+351914248296</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>ggboxekickboxing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>L1778</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Jazzy Fight Club (Estádio da Luz)</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>+351217161774</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>L1779</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Associação de Boxe Paulo Seco</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>+351965593149</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>associacaoboxepauloseco@gmail.com</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>L1780</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>John Style Muay Thai</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>+351918725290</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>L1781</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Academia Jorge Pina</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>+351214091807</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>jorgepina.associacao@gmail.com</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>L1782</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Areeiro</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>+351934752010</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>L1783</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Saldanha</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>+351934082824</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>saldanha@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>L1784</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Ginásio KO - SLO (Boxe, Kickboxing &amp; Jiu-Jitsu)</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>+351926372441</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>L1785</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing EXPO</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>+351962144188</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>expo@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>L1786</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Carnide</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>+351934175777</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>carnide@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>L1787</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Alto dos moinhos</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>+351910370776</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>altodosmoinhos@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>L1789</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Brave Fight Team</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>+351217271816</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>brave-fightgym@outlook.pt</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>L1790</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Lisbon Gymnastics Club</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>+351213154002</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>geral@lgc.pt</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>L1791</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Academia Nova União Lisboa - JiuJitsu</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>+351911083709</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>L1792</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Health and Fun</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>+351934623202</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>L1793</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Restelo</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>+351915011863</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>restelo@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>L1794</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Absolute Health Club</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>+351968155833</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>L1795</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Chiado Training Club</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>+351935422128</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>info@chiadotrainingclub.com</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>L1796</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Campolide Atlético Clube</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>+351213854538</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>L1797</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Clube de Boxe de Santo António</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>+351969179624</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>info@jfsantoantonio.pt</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>L1798</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Escola de Boxe da Outurela</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>+351961144103</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>L1799</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Prime Fight Club</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>+351918130737</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>L1800</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Alpha Box CT</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>+351939045464</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>L1801</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Alfragide</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>+351926228125</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>alfragide@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>L1803</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Action Black Parque das Nações</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>+351915207584</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>manager.portugal@actionblack.pt</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>L1804</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>ACM Lisbon</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>+351934243035</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>L1805</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Bogas Team Fight Center</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>+351914367087</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>L1808</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Barao team</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>+351932818776</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>baraoteam</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>L1809</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>IC - Personal Trainer</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>+351913560261</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr"/>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>L1810</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Zen Center</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>+351935106777</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>L1811</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing Miraflores</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>+351913947217</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>miraflores@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr"/>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>L1812</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Academia Ricardo Fernandes</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>+351939091155</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>L1813</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Magic Form</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>+351926156820</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="inlineStr"/>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>L1815</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Academia Life Club</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>+351213934020</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr"/>
+      <c r="F952" t="inlineStr"/>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>L1816</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Fight Squad Store</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>+351914966198</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>info@fightsquadstore.com</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr"/>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>L1817</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Higgs Academy Fight Team Defesa Pessoal</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>+351919931007</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="inlineStr"/>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>L1818</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>BPT Moscavide</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>+351961500614</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr"/>
+      <c r="F955" t="inlineStr"/>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>L1820</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>STAT Campo Pequeno</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>+351938867036</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr"/>
+      <c r="F956" t="inlineStr"/>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>L1821</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>CT Portugal Gold Team Pontinha</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>+351934302786</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr"/>
+      <c r="F957" t="inlineStr"/>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>L1822</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Blue House Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>+351968203866</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr"/>
+      <c r="F958" t="inlineStr"/>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr"/>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>L1823</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Estilo MMA Lisboa - Loja de boxe, Muay Thai, MMA e Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>+351913671093</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr"/>
+      <c r="F959" t="inlineStr"/>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>L1824</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Alliance Jiu Jitsu Saldanha</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>+351934468931</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr"/>
+      <c r="F960" t="inlineStr"/>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr"/>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>L1825</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>All About Jiu-Jitsu</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>+351913329778</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr"/>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>L1826</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Jiu Jitsu - Gracie Barra Ameixoeira</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>+351926371933</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr"/>
+      <c r="F962" t="inlineStr"/>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>L1827</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Five Elements Jiu-Jitsu Benfica</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>+351915297080</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr"/>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr"/>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>L1828</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Gracie Barra Braço de Prata</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>+351934268683</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>geral@gbbracodeprata.pt</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>L1829</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Saitama jiu jitsu team Portugal campolide</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>+351937443787</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>contacto@saitamabjj.com, jane@framer.com</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr"/>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>L1831</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Holdz Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>+351920768502</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr"/>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>holdzjiujitsu</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>L1832</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Clube de Praticantes de Jiu-Jitsu Brasileiro Lisboa</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>+351934444293</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr"/>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>L1833</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Bitim Grappling Jiu-jítsu</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>+351926390865</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr"/>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr"/>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>L1835</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>SKEMA Kampfkunst Zürich Oerlikon</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>+41443120818</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>oerlikon@skema.ch</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>L1837</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Traditional Martial Arts Taekwondo Switzerland</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>+41434228877</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr"/>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr"/>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>L1838</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>ZI RAN WU YI KUNG FU SCHULE</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>+41788809999</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr"/>
+      <c r="F971" t="inlineStr"/>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>L1839</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>360 Martial Arts</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>+41444311134</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>info@360martialarts.ch</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>L1840</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>TATAME 8000 - Fight Collective Zürich</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>+41767728171</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>info@tatame8000.ch</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>L1841</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>SKEMA Kampfkunst Zürich Altstetten</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>+41444014042</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>zuerich@skema.ch</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>L1842</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Taekwon-Do Center Zurich Terranova</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>+41762647477</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>center@taekwondo-terranova.com, m.delena@taekwondo-zuerich.ch</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>L1843</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>ALYART JIU-JITSU - BJJ Zürich - Brazilian Jiu-Jitsu Zürich</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>+41789434345</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com, 8c4075d5481d476e945486754f783364@sentry.io, 79baaa8e09c746d2b7401643b99792e0@sentry.wixpress.com, dd0a55ccb8124b9c9d938e3acf41f8aa@sentry.wixpress.com, c183baa23371454f99f417f6616b724d@sentry.wixpress.com, 9a65e97ebe8141fca0c4fd686f70996b@sentry.wixpress.com, 460ff4620fa44cba8df530afde949785@sentry.wixpress.com, ed436f5053144538958ad06a5005e99a@sentry.wixpress.com, 18d2f96d279149989b95faf0a4b41882@sentry-next.wixpress.com, 2062d0a4929b45348643784b5cb39c36@sentry.wixpress.com, 78f7996315bc402f9dcb8a2f974b82d1@sentry.wixpress.com, 8eb368c655b84e029ed79ad7a5c1718e@sentry.wixpress.com, a18507e8883842d8a1ba47257fee81ac@sentry.wixpress.com, 271e9fa3230b4eec94b02bf95780f5f2@sentry.wixpress.com, 5d1795a2db124a268f1e1bd88f503500@sentry.wixpress.com, beispiel@email.com</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>L1844</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Helveticsport Muay Thai Schule Zürich</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>+41797778888</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>uzun@uzun.ch</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>L1845</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>chinese martial-arts and yoga</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>+41796430854</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>info@ma-academy.ch</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>L1846</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Vacirca Academy Gracie Jiu-Jitsu Zürich</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>+41794150808</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr"/>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>L1847</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>STREETS FIGHT CLUB</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>+41767893015</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr"/>
+      <c r="F980" t="inlineStr"/>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>L1848</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Kampfkunstschmiede Zürich-Oerlikon</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>+41764739731</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>anna@kampfkunstschmiede.ch</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr"/>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>L1849</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>BJJ Lab Zürich</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>+41766971885</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>info@bjjlab.ch</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr"/>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>L1851</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Functional Fighting</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>+41445201050</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>office@functionalfighting.ch</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr"/>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>L1852</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Alpha Academy Zürich</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>+41795512098</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr"/>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>L1853</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Kickboxing Schule Zürich / Kickboxen seit 1993</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>+41794040729</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>info@kickboxing-zh.ch</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr"/>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>L1854</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Tiago De Paula BJJ</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>+41789503999</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr"/>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>L1855</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Adamantium Bjj Zürich</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>+41788265056</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>adamantiumbjj@gmail.com</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr"/>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>L1857</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Peter Mettler MOTU Martial Arts Zürich</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>+41762029015</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>info@mo-tu.ch</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>L1858</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Zürich Taekwondo Imperial</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>+41765645548</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr"/>
+      <c r="F989" t="inlineStr"/>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>L1859</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Kim Dojo Shotokan Karate Klub</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>+41449367184</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr"/>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>L1862</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Asia Budo Center</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>+41433115150</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>info@asiabudocenter.ch</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr"/>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>L1864</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Shukokai Seikenkan Karate Do Zürich</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>+41442723440</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr"/>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>L1865</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Chin Woo Kung Fu Center Zürich</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>+41796830162</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>info@chinwoo-zuerich.ch</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>L1866</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Shobukan Goju Ryu Karate Club Zürich</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>+41794787881</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr"/>
+      <c r="F994" t="inlineStr"/>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr"/>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>L1868</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Asgard Sport Academy GmbH</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>+41762173056</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>info@asgardsportacademy.ch</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr"/>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>L1869</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Bujutsu School Zürich</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>+41792675832</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr"/>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr"/>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>L1870</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Aiki-Kai Zürich</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>+41442725434</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>webadmin@aikikai-zuerich.ch</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr"/>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>L1871</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>SUN WU Zürich</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>+41794309966</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr"/>
+      <c r="F998" t="inlineStr"/>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr"/>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>L1873</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Checkmat Zurich Brazilian Jiu-Jitsu</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>+41775127970</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr"/>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>L1874</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Karate Akademie Zürich</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>+41442626272</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>L1875</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>CSF – Blue Barrel Gym | Boxen &amp; Thaiboxen Zürich Oerlikon</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>+41795854884</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr"/>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>L1876</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Budo Schule Samurai</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>+41443022623</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>kfeierabend@bluewin.ch</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>L1877</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Carlson Gracie Zurich Brasilien jiu jitsu</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>+41798888613</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>info@carlsongracie.ch</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>L1878</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Taekwondo Schule Schweiz International</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>+41764353675</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>info@swisstkd.ch</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr"/>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>L1879</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>KUNG FU SCHULE MARTIN SEWER</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>+41848788887</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr"/>
+      <c r="F1005" t="inlineStr"/>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>L1880</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>MKC Kickboxing Academy GmbH</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>+41444514488</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr"/>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>L1881</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>RYUEI-RYU Zürich-Suisse</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>+41784208868</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>fredyminano@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr"/>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>L1882</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Shotokan Karateschule Zürich</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>+41435455188</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>info@swisskarate.ch, wallisellen@swisskarate.ch</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>L1884</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>MEIN TEMPEL - Kung Fu Schule</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>+41793651778</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>user@domain.com, info@meintempel.ch</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>L1885</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Vera bjj kids</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>+41765053290</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>info@alphamaxbjj.ch</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr"/>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>L1887</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Box Club Zürich</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>+41763709747</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr"/>
+      <c r="F1011" t="inlineStr"/>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>L1888</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Box Dich Fit Zürich</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>+41765974730</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>chris@boxdichfit.ch</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>L1889</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Dream Team Boxing</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>+41766757122</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>pfluegel007@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>L1891</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Private Boxing Zürich</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>+41768441110</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>giacomo@privateboxingzurich.ch</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>L1892</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>i-Fight — Muay Thai Zürich</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>+41782545003</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>info@i-fight.ch</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr"/>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>L1893</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Jäger Boxing</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>+41786955152</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>info@jaegerboxing.ch</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr"/>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>L1895</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Old School BoxClub Zürich</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>+41799067063</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr"/>
+      <c r="F1017" t="inlineStr"/>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>L1896</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Lionsoul Zürich 24H Fitness</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>+41449190077</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>info@lionsoul.ch</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>L1897</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Reactics - FightForge / Kampfsport Friesenberg</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>+41793720005</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>info@reactics.ch</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr"/>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>L1899</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>America Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>+41766144441</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>info@americaboxing.ch</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr"/>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>L1901</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Power Sports Club / Kickboxen Zürich</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>+41445434748</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>user@domain.com, nora.ermatinger@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>L1903</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Ringside Gym</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>+41763300030</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>benutzer@domain.com, info@ringsidegym.ch, info@ringsidegym.ch</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>L1905</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Jens Krull Boxing - Fitness - Boxing - Personal Training - Z</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>+41793070471</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>L1906</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kampfsport Trainingcenter Zürich - Fight-World - Kampfsport </t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>+41792874005</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>L1907</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Hit4Fit</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>+41796014265</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>info@hit4fit.ch</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr"/>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>L1908</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Thaiboxschmiede Zürich</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>+41799351012</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>L1909</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Asia Sport Center AG</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>+41443500555</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>info@asc.ch</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>L1910</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>BYTX Personal Training Studio</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>+41789211273</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>info@bytxstudio.com</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>L1911</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Frota Academy | Jiu-Jitsu | MMA | BJJ Kids | Muay Thai | Gra</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>+41763686293</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>info@frota-team.ch</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>L1913</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Frauen-Boxen Zürich Wiedikon</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>+41764279969</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>info@frauen-boxen.ch</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>L1914</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Strike Zone</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>+41798585472</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>info@strike-zone.ch</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>L1915</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>nextlevel Sports Club</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>+41445248149</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>hello@nlsc.ch</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>L1916</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Box Center Glattbrugg</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>+41796665901</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>L1917</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Profight-Gym</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>+41788314989</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>duebendorf@fabrik11.ch</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>L1918</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Halle 41 Fitness Zürich West</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>+41433668866</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>receptionzuerich@halle41.ch</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>L1919</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Budocenter - Kickboxen- and Taekwondo Center Zurich</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>+41763224848</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>L1920</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Boxclub Knockout</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>+41763791015</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>info@boxclub-knockout.ch</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr"/>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>L1921</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>FAIRPLAY Fitness und Kampfsport Studio Ivo Furrer</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>+41439601640</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>info@fit4fight.ch</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>L1922</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Personaltraining BoxWorld</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>+41765748082</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>info@boxworld.ch</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>L1923</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>One Team Gym</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>+41764038910</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>support@webador.de, info@oneteamgym.ch</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr"/>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>L1924</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>All Style Fighting Zürich</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>+41794008656</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr"/>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>L1925</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Klub der Sportfreunde AG</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>+41764944374</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>info@klubdersportfreunde.ch, info@klubdersportfreunde.de</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr"/>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>L1926</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Zürich Gym - hurt locker</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>+41797438478</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>info@zuerichgym.ch</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>L1927</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Nippon Training</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>+41447341111</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>info@haris.ch</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>L1929</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>David Gym ZH-West</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>+41433111230</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>info@davidgym.ch</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>L1931</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>STRIKING Studio</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>+41772885269</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>L1932</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>HOGA • Brazilian Jiu Jitsu • Muay Thai</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>+41774027981</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr"/>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>L1933</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Unit-Group Fightsport</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>+41779385870</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr"/>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>L1934</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Natthapong Gym</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>+41799018050</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>ebguxriva@zfa.pbz, vasb@angguncbat-tlz.pu</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>L1936</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Renovazio Muay Thai Thaiboxschule</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>+41763166580</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>mustermann@beispiel.de</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>L1937</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Indigo Fitness Club Zürich</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>+41442121200</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>zurich@indigofitness.ch</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>L1938</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>FriendlyFire Dojo Kampfsport Club</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>+41796137092</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr"/>
+      <c r="F1052" t="inlineStr"/>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>L1939</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Atos Jiu Jitsu Zürich</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>+41764758182</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>info@atosbjjzurich.com</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>L1940</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>CR Academy Brazilian Jiu-Jitsu</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>+41789284118</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr"/>
+      <c r="F1054" t="inlineStr"/>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>L1941</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Ju-Jitsu Zürich</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>+41763210346</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr"/>
+      <c r="F1055" t="inlineStr"/>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>L1942</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Chaz BJJ Zürich</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>+41765690359</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>chaz.bjj.zh@gmail.com, info@mysite.com</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>L1943</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Sequência BJJ Zürich</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>+41798148600</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr"/>
+      <c r="F1057" t="inlineStr"/>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -29423,7 +29423,7 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | IG profile not found (2026-10-25)</t>
         </is>
       </c>
       <c r="H890" t="inlineStr"/>
@@ -31207,7 +31207,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | IG follow=ok dm=sent (Daily 2026-10-25)</t>
         </is>
       </c>
       <c r="H946" t="inlineStr"/>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | IG follow=ok dm=sent (Daily 2026-10-25)</t>
         </is>
       </c>
       <c r="H966" t="inlineStr"/>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -21959,7 +21959,7 @@
       <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL FIXED (multi-address cell -&gt; best valid) | EMAIL VERIFIED (domain match) | COMPLETE: email sent (Daily 2026-10-25)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL FIXED (multi-address cell -&gt; best valid) | EMAIL VERIFIED (domain match) | COMPLETE: email sent (Daily 2026-10-25) | EMAIL FAILED (bounce confirmed 2026-10-26)</t>
         </is>
       </c>
       <c r="H656" t="inlineStr"/>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1057"/>
+  <dimension ref="A1:H1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11473,7 +11473,7 @@
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
@@ -11635,7 +11635,7 @@
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
@@ -11703,7 +11703,7 @@
       <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H340" t="inlineStr"/>
@@ -11737,7 +11737,7 @@
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H341" t="inlineStr"/>
@@ -11801,7 +11801,7 @@
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
@@ -12031,7 +12031,7 @@
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
@@ -12585,7 +12585,7 @@
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H367" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H370" t="inlineStr"/>
@@ -12883,7 +12883,7 @@
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H383" t="inlineStr"/>
@@ -13361,7 +13361,7 @@
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H391" t="inlineStr"/>
@@ -13459,7 +13459,7 @@
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H394" t="inlineStr"/>
@@ -13655,7 +13655,7 @@
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H400" t="inlineStr"/>
@@ -13889,7 +13889,7 @@
       <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H407" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H412" t="inlineStr"/>
@@ -14085,7 +14085,7 @@
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H413" t="inlineStr"/>
@@ -14119,7 +14119,7 @@
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H414" t="inlineStr"/>
@@ -14153,7 +14153,7 @@
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H415" t="inlineStr"/>
@@ -29137,7 +29137,7 @@
       <c r="F881" t="inlineStr"/>
       <c r="G881" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H881" t="inlineStr"/>
@@ -29231,7 +29231,7 @@
       <c r="F884" t="inlineStr"/>
       <c r="G884" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (day12 QA: email not verifiable on the lead own site)</t>
         </is>
       </c>
       <c r="H884" t="inlineStr"/>
@@ -29259,13 +29259,13 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>sdbenfica@vma.com.pt, alfragide@vma.com.pt, email@dominio.pt</t>
+          <t>sdbenfica@vma.com.pt</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
       <c r="G885" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; sdbenfica@vma.com.pt; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H885" t="inlineStr"/>
@@ -29329,7 +29329,7 @@
       <c r="F887" t="inlineStr"/>
       <c r="G887" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (malformed email cell: no usable address)</t>
         </is>
       </c>
       <c r="H887" t="inlineStr"/>
@@ -29547,7 +29547,7 @@
       <c r="F894" t="inlineStr"/>
       <c r="G894" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (malformed email cell: no usable address)</t>
         </is>
       </c>
       <c r="H894" t="inlineStr"/>
@@ -29729,13 +29729,13 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>info@anks.pt, u003einfo@anks.pt</t>
+          <t>info@anks.pt</t>
         </is>
       </c>
       <c r="F900" t="inlineStr"/>
       <c r="G900" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@anks.pt; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H900" t="inlineStr"/>
@@ -29799,7 +29799,7 @@
       <c r="F902" t="inlineStr"/>
       <c r="G902" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H902" t="inlineStr"/>
@@ -29827,13 +29827,13 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>hussainmazhar558@gmail.com, info@tehreembco.com</t>
+          <t>info@tehreembco.com</t>
         </is>
       </c>
       <c r="F903" t="inlineStr"/>
       <c r="G903" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@tehreembco.com; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H903" t="inlineStr"/>
@@ -29957,7 +29957,7 @@
       <c r="F907" t="inlineStr"/>
       <c r="G907" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H907" t="inlineStr"/>
@@ -30055,7 +30055,7 @@
       <c r="F910" t="inlineStr"/>
       <c r="G910" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H910" t="inlineStr"/>
@@ -30183,7 +30183,7 @@
       <c r="F914" t="inlineStr"/>
       <c r="G914" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (malformed email cell: no usable address)</t>
         </is>
       </c>
       <c r="H914" t="inlineStr"/>
@@ -30277,7 +30277,7 @@
       <c r="F917" t="inlineStr"/>
       <c r="G917" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H917" t="inlineStr"/>
@@ -30533,7 +30533,7 @@
       <c r="F925" t="inlineStr"/>
       <c r="G925" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H925" t="inlineStr"/>
@@ -30597,7 +30597,7 @@
       <c r="F927" t="inlineStr"/>
       <c r="G927" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H927" t="inlineStr"/>
@@ -30631,7 +30631,7 @@
       <c r="F928" t="inlineStr"/>
       <c r="G928" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H928" t="inlineStr"/>
@@ -30665,7 +30665,7 @@
       <c r="F929" t="inlineStr"/>
       <c r="G929" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H929" t="inlineStr"/>
@@ -30699,7 +30699,7 @@
       <c r="F930" t="inlineStr"/>
       <c r="G930" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H930" t="inlineStr"/>
@@ -30733,7 +30733,7 @@
       <c r="F931" t="inlineStr"/>
       <c r="G931" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H931" t="inlineStr"/>
@@ -30891,7 +30891,7 @@
       <c r="F936" t="inlineStr"/>
       <c r="G936" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H936" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       <c r="F938" t="inlineStr"/>
       <c r="G938" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H938" t="inlineStr"/>
@@ -31113,7 +31113,7 @@
       <c r="F943" t="inlineStr"/>
       <c r="G943" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H943" t="inlineStr"/>
@@ -31425,7 +31425,7 @@
       <c r="F953" t="inlineStr"/>
       <c r="G953" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H953" t="inlineStr"/>
@@ -31759,7 +31759,7 @@
       <c r="F964" t="inlineStr"/>
       <c r="G964" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H964" t="inlineStr"/>
@@ -31787,13 +31787,13 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>contacto@saitamabjj.com, jane@framer.com</t>
+          <t>contacto@saitamabjj.com</t>
         </is>
       </c>
       <c r="F965" t="inlineStr"/>
       <c r="G965" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; contacto@saitamabjj.com; name/site slug match) | EXCLUDED (day12 QA: email not verifiable on the lead own site)</t>
         </is>
       </c>
       <c r="H965" t="inlineStr"/>
@@ -31921,7 +31921,7 @@
       <c r="F969" t="inlineStr"/>
       <c r="G969" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H969" t="inlineStr"/>
@@ -32015,7 +32015,7 @@
       <c r="F972" t="inlineStr"/>
       <c r="G972" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H972" t="inlineStr"/>
@@ -32049,7 +32049,7 @@
       <c r="F973" t="inlineStr"/>
       <c r="G973" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H973" t="inlineStr"/>
@@ -32083,7 +32083,7 @@
       <c r="F974" t="inlineStr"/>
       <c r="G974" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H974" t="inlineStr"/>
@@ -32111,13 +32111,13 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>center@taekwondo-terranova.com, m.delena@taekwondo-zuerich.ch</t>
+          <t>center@taekwondo-terranova.com</t>
         </is>
       </c>
       <c r="F975" t="inlineStr"/>
       <c r="G975" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; center@taekwondo-terranova.com; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H975" t="inlineStr"/>
@@ -32151,7 +32151,7 @@
       <c r="F976" t="inlineStr"/>
       <c r="G976" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (malformed email cell: no usable address)</t>
         </is>
       </c>
       <c r="H976" t="inlineStr"/>
@@ -32185,7 +32185,7 @@
       <c r="F977" t="inlineStr"/>
       <c r="G977" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H977" t="inlineStr"/>
@@ -32219,7 +32219,7 @@
       <c r="F978" t="inlineStr"/>
       <c r="G978" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H978" t="inlineStr"/>
@@ -32313,7 +32313,7 @@
       <c r="F981" t="inlineStr"/>
       <c r="G981" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H981" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
       <c r="F983" t="inlineStr"/>
       <c r="G983" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H983" t="inlineStr"/>
@@ -32445,7 +32445,7 @@
       <c r="F985" t="inlineStr"/>
       <c r="G985" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H985" t="inlineStr"/>
@@ -32543,7 +32543,7 @@
       <c r="F988" t="inlineStr"/>
       <c r="G988" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H988" t="inlineStr"/>
@@ -32637,7 +32637,7 @@
       <c r="F991" t="inlineStr"/>
       <c r="G991" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H991" t="inlineStr"/>
@@ -32701,7 +32701,7 @@
       <c r="F993" t="inlineStr"/>
       <c r="G993" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H993" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
       <c r="F995" t="inlineStr"/>
       <c r="G995" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H995" t="inlineStr"/>
@@ -32829,7 +32829,7 @@
       <c r="F997" t="inlineStr"/>
       <c r="G997" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H997" t="inlineStr"/>
@@ -33017,7 +33017,7 @@
       <c r="F1003" t="inlineStr"/>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr"/>
@@ -33051,7 +33051,7 @@
       <c r="F1004" t="inlineStr"/>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1004" t="inlineStr"/>
@@ -33173,13 +33173,13 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>info@swisskarate.ch, wallisellen@swisskarate.ch</t>
+          <t>info@swisskarate.ch</t>
         </is>
       </c>
       <c r="F1008" t="inlineStr"/>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@swisskarate.ch; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1008" t="inlineStr"/>
@@ -33207,13 +33207,13 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>user@domain.com, info@meintempel.ch</t>
+          <t>info@meintempel.ch</t>
         </is>
       </c>
       <c r="F1009" t="inlineStr"/>
       <c r="G1009" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@meintempel.ch; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1009" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       <c r="F1012" t="inlineStr"/>
       <c r="G1012" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr"/>
@@ -33379,7 +33379,7 @@
       <c r="F1014" t="inlineStr"/>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1014" t="inlineStr"/>
@@ -33413,7 +33413,7 @@
       <c r="F1015" t="inlineStr"/>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr"/>
@@ -33447,7 +33447,7 @@
       <c r="F1016" t="inlineStr"/>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1016" t="inlineStr"/>
@@ -33511,7 +33511,7 @@
       <c r="F1018" t="inlineStr"/>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1018" t="inlineStr"/>
@@ -33545,7 +33545,7 @@
       <c r="F1019" t="inlineStr"/>
       <c r="G1019" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       <c r="F1020" t="inlineStr"/>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr"/>
@@ -33613,7 +33613,7 @@
       <c r="F1021" t="inlineStr"/>
       <c r="G1021" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (malformed email cell: no usable address)</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr"/>
@@ -33641,13 +33641,13 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>benutzer@domain.com, info@ringsidegym.ch, info@ringsidegym.ch</t>
+          <t>info@ringsidegym.ch</t>
         </is>
       </c>
       <c r="F1022" t="inlineStr"/>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@ringsidegym.ch; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr"/>
@@ -33741,7 +33741,7 @@
       <c r="F1025" t="inlineStr"/>
       <c r="G1025" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       <c r="F1027" t="inlineStr"/>
       <c r="G1027" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr"/>
@@ -33839,7 +33839,7 @@
       <c r="F1028" t="inlineStr"/>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr"/>
@@ -33873,7 +33873,7 @@
       <c r="F1029" t="inlineStr"/>
       <c r="G1029" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1029" t="inlineStr"/>
@@ -33907,7 +33907,7 @@
       <c r="F1030" t="inlineStr"/>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr"/>
@@ -33941,7 +33941,7 @@
       <c r="F1031" t="inlineStr"/>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr"/>
@@ -34039,7 +34039,7 @@
       <c r="F1034" t="inlineStr"/>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       <c r="F1035" t="inlineStr"/>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr"/>
@@ -34137,7 +34137,7 @@
       <c r="F1037" t="inlineStr"/>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr"/>
@@ -34171,7 +34171,7 @@
       <c r="F1038" t="inlineStr"/>
       <c r="G1038" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1038" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
       <c r="F1039" t="inlineStr"/>
       <c r="G1039" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1039" t="inlineStr"/>
@@ -34233,13 +34233,13 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>support@webador.de, info@oneteamgym.ch</t>
+          <t>info@oneteamgym.ch</t>
         </is>
       </c>
       <c r="F1040" t="inlineStr"/>
       <c r="G1040" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@oneteamgym.ch; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1040" t="inlineStr"/>
@@ -34297,13 +34297,13 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>info@klubdersportfreunde.ch, info@klubdersportfreunde.de</t>
+          <t>info@klubdersportfreunde.ch</t>
         </is>
       </c>
       <c r="F1042" t="inlineStr"/>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; info@klubdersportfreunde.ch; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       <c r="F1043" t="inlineStr"/>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr"/>
@@ -34371,7 +34371,7 @@
       <c r="F1044" t="inlineStr"/>
       <c r="G1044" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1044" t="inlineStr"/>
@@ -34405,7 +34405,7 @@
       <c r="F1045" t="inlineStr"/>
       <c r="G1045" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1045" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       <c r="F1049" t="inlineStr"/>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (malformed email cell: no usable address)</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr"/>
@@ -34563,7 +34563,7 @@
       <c r="F1050" t="inlineStr"/>
       <c r="G1050" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EXCLUDED (day12 QA: placeholder/example domain)</t>
         </is>
       </c>
       <c r="H1050" t="inlineStr"/>
@@ -34597,7 +34597,7 @@
       <c r="F1051" t="inlineStr"/>
       <c r="G1051" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr"/>
@@ -34661,7 +34661,7 @@
       <c r="F1053" t="inlineStr"/>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-26)</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr"/>
@@ -34749,13 +34749,13 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>chaz.bjj.zh@gmail.com, info@mysite.com</t>
+          <t>chaz.bjj.zh@gmail.com</t>
         </is>
       </c>
       <c r="F1056" t="inlineStr"/>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | EMAIL FIXED (multi-address cell -&gt; chaz.bjj.zh@gmail.com; name-matched webmail)</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr"/>
@@ -34789,6 +34789,544 @@
         </is>
       </c>
       <c r="H1057" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>L1947</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Portugal Judo Club</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>+351213884011</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr"/>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>L1952</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Crossfit Move On</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>+351934324900</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr"/>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>L1953</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>FACTORY GYM OF PHYSICAL</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>+351961781609</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr"/>
+      <c r="F1060" t="inlineStr"/>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>L1955</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Zarka Jiu-Jitsu Academy</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>+351934937540</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr"/>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>L1956</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>BPT Arroios Nasser Camará</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>+351925393575</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="inlineStr"/>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>L1957</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>RIO-SUL-BJJ</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>+351968269888</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr"/>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>riosulventeira</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | IG follow=ok dm=sent (Daily 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>L1958</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Connect Belt Team Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>+351926442202</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr"/>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>connectbeltteamjiujitsu</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | IG follow=ok dm=no-msg-btn (Daily 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>L1959</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>RIO21 - Academia de Jiu-jitsu</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>+351916995642</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr"/>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>rio21.lisboa</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | IG follow=no-btn dm=sent (Daily 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>L1960</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Fight Nation Santa Engracia</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>+351924093064</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr"/>
+      <c r="F1066" t="inlineStr"/>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>L1963</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Hooked HPC</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>+41791251536</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>hooked.hpc@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr"/>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>L1965</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>CrossFit Zurich</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>+41444310669</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>info@crossfitzuerich.ch</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr"/>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | EMAIL FIXED (multi-address cell -&gt; info@crossfitzuerich.ch; exact website domain) | COMPLETE: email sent (Daily 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>L1966</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Kensho Sports Baden</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>+41791757393</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>info@kensho-sports.com</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr"/>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | COMPLETE: email sent (Daily 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>L1968</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Ezinho BJJ | Jiu Jitsu Classes in Wallisellen</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>+41791975873</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>ezinho_bjj</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | IG follow=ok dm=sent (Daily 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>L1969</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Judo und Ju-Jitsu Club Weisse Löwen Zürich</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>+41766994904</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="inlineStr"/>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>L1970</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Van Led BJJ</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>+41764707818</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="inlineStr"/>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>L1971</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Roger Gracie Brazilian Jiu Jitsu BJJ Zürich</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>+41763774216</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="inlineStr"/>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>L1972</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>2Fight Zürich - Krav Maga Center</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>+41795401234</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="inlineStr"/>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1074"/>
+  <dimension ref="A1:H1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -35328,6 +35328,996 @@
       </c>
       <c r="H1074" t="inlineStr"/>
     </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>L1978</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Family Martial Arts Centre (Denton)</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>+447857989516</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="inlineStr"/>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>L1980</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>GKKC Club</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>+447891653841</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr"/>
+      <c r="F1076" t="inlineStr"/>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>L1983</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Ken Shu Dojo Karate Whitefield</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>+447886307454</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr"/>
+      <c r="F1077" t="inlineStr"/>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>L1985</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Shins TKD Academy</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>+441618487426</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>tw.shin@shinsacademytkd.co.uk</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr"/>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>L1986</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Jeet Kune Do</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>+441619987062</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="inlineStr"/>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>L1988</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Hybrid Mixed Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>+447946813680</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>jamie@hybridmma.academy</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr"/>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>L1989</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Central Performance Centre - BJJ &amp; MMA in Stockport</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>+441617060660</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>info@centralperformancecentre.co.uk</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr"/>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>L1990</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Daywalkers MMA</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>+447946329261</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr"/>
+      <c r="F1082" t="inlineStr"/>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>L1991</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>DEMAA</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>+447866952066</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr"/>
+      <c r="F1083" t="inlineStr"/>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>L1992</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>AQF Sports | Boxing, MMA, Gym, Fitness Equipment &amp; Accessori</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>+441204704130</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>info@aqfsports.co.uk</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr"/>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>L1993</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>2 Technical Muay Thai</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>+447920002233</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr"/>
+      <c r="F1085" t="inlineStr"/>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>L1994</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>SRMT</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>+447429496791</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>info@rakhangmuaythai.co.uk</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr"/>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>L1995</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>All Powers Gym</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>+447824996443</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>allpowersgym@outlook.com</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr"/>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>L1996</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Evade Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>+441457833987</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>evademartialarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr"/>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>L1997</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Cherry Blossom BJJ &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>+447837006554</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>cherryblossombjj@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr"/>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>L1998</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Manchester Brazilian Jiu-Jitsu: Bushido BJJ</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>+448606825876</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>manchesterbjj@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr"/>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>L1999</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Grapple House BJJ</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>+447972194576</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr"/>
+      <c r="F1091" t="inlineStr"/>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>L2000</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>UoM Jiu-Jitsu Club</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>+441615294444</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr"/>
+      <c r="F1092" t="inlineStr"/>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>L2001</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Sale Ju-Jitsu Academy</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>+447469699121</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>info@salejujitsu.co.uk</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr"/>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>L2003</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Renzo Gracie NH</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>+446037772775</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr"/>
+      <c r="F1094" t="inlineStr"/>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>L2004</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Manchester jujitsu club</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>+447813897021</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>johnshortt@manchesterjujitsuclub.com</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr"/>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>L2007</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Dún Laoghaire Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>+353852214824</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr"/>
+      <c r="F1096" t="inlineStr"/>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>L2009</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Brazier Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>+353831304155</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>hello.ie@brazierjiujitsu.com</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr"/>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>L2010</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Tallaght Martial Arts And Fitness Centre</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>+353868388478</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>tallaghtmartialarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr"/>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>L2011</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Silverback Jiu Jitsu Academy</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>+353872420647</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>silverbackjiujitsuacademy@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr"/>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>L2012</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Gracie Jiu-Jitsu Baldoyle | Ralph Gracie Ireland</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>+353851151123</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr"/>
+      <c r="F1100" t="inlineStr"/>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>L2013</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Krav-Maga Bukan Dublin</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>+353838571853</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>contact@kravmaga-ireland.com</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr"/>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>L2014</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>UCD Karate</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>+35317163839</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr"/>
+      <c r="F1102" t="inlineStr"/>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>L2018</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>St Matthews Boxing Club</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>+35316426008</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr"/>
+      <c r="F1103" t="inlineStr"/>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>L2021</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Blackrock Health and Fitness</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>+353879141704</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr"/>
+      <c r="F1104" t="inlineStr"/>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>L2022</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Cie Boxing Club</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>+353852024171</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr"/>
+      <c r="F1105" t="inlineStr"/>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1105"/>
+  <dimension ref="A1:H1235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -824,7 +824,11 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>@judokitaro</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Judo Kitaro! \n\n\n\nwe make custom mar"]} | WA sent (Day 6)</t>
@@ -1018,7 +1022,11 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>@gracielisboa_jiujitsu</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Gracie Lisboa! \n\n\n\nmartial arts &amp; s"]} | WA sent (Day 6)</t>
@@ -2534,7 +2542,11 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>@themartialartsplace</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -2564,7 +2576,11 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>@islingtonmartialarts</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
@@ -2752,7 +2768,11 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>@koryotkdacademy</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
@@ -3008,7 +3028,11 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>@chingymac10</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
@@ -3298,7 +3322,11 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>@gurumu_taekwondo</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -3328,7 +3356,11 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>@triumfit_bmaa</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -3392,7 +3424,11 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>@silatopencircle_international</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -3422,7 +3458,11 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>@eastlondonkempo</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -3682,7 +3722,11 @@
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>@kru_nuat</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -4052,7 +4096,11 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>@lucianocristovamacademy</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -4802,7 +4850,11 @@
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>@krav_maga_manchester_fekm</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -5080,7 +5132,11 @@
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>@aptaekwondoacademy</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -5468,7 +5524,11 @@
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>@jbbba_manchester</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -6676,7 +6736,11 @@
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>@hive_bjj</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -6966,7 +7030,11 @@
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>@AdrenalineCombatives</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-21)</t>
@@ -7094,7 +7162,11 @@
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>@junglebjjdublin</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -7192,7 +7264,11 @@
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>@alexandrefitness</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -8194,10 +8270,14 @@
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>@bextremefightclub</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -8292,10 +8372,14 @@
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>@krav4lifeacademy</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG profile not found (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -8356,10 +8440,14 @@
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>@teamryano</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -8582,10 +8670,14 @@
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>@beatboxfitnessdublin</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG profile not found (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
@@ -8894,10 +8986,14 @@
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>@monkstownbcdub</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
@@ -9146,10 +9242,14 @@
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>@ufcgymdublin1</t>
+        </is>
+      </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
@@ -9270,10 +9370,14 @@
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>@westsidegymsdublin</t>
+        </is>
+      </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
@@ -9488,10 +9592,14 @@
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>@python_mma_1</t>
+        </is>
+      </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
@@ -10562,10 +10670,14 @@
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>@shoshinaikidoamsterdam</t>
+        </is>
+      </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -10724,10 +10836,14 @@
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>@wingchunfederatie</t>
+        </is>
+      </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
@@ -10912,10 +11028,14 @@
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>@abovboxingamsterdam</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
@@ -11342,10 +11462,14 @@
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>@blanchardboxingcoach</t>
+        </is>
+      </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=clicked dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
@@ -11862,10 +11986,14 @@
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>@escpkaratewado</t>
+        </is>
+      </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=clicked dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
@@ -12058,10 +12186,14 @@
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>@dojogrenelleparis</t>
+        </is>
+      </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=clicked dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
@@ -12088,10 +12220,14 @@
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>@seibukanparis12</t>
+        </is>
+      </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=clicked dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
@@ -12220,10 +12356,14 @@
           <t>contact.senyuu@gmail.com</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>@teamsenyuukarate</t>
+        </is>
+      </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched) | IG follow=clicked dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
@@ -12514,10 +12654,14 @@
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>@lwspakmei</t>
+        </is>
+      </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG handle mismatch, not contacted (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H365" t="inlineStr"/>
@@ -12846,7 +12990,11 @@
           <t>itf.tkd.paris@gmail.com</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>@eliottsaku</t>
+        </is>
+      </c>
       <c r="G375" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -12974,7 +13122,11 @@
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>@taijitsuclubsr75</t>
+        </is>
+      </c>
       <c r="G379" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -13004,7 +13156,11 @@
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>@taikiclub</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -13064,7 +13220,11 @@
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>@dojoninjaparis</t>
+        </is>
+      </c>
       <c r="G382" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -13162,7 +13322,11 @@
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>@oshukai_paris</t>
+        </is>
+      </c>
       <c r="G385" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -13260,7 +13424,11 @@
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>@striking_paris15</t>
+        </is>
+      </c>
       <c r="G388" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -13984,7 +14152,11 @@
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>@fitnessparkclichy</t>
+        </is>
+      </c>
       <c r="G410" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -14218,10 +14390,14 @@
           <t>contact@bizot.org</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>@usmetro_bizot</t>
+        </is>
+      </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H417" t="inlineStr"/>
@@ -14282,7 +14458,11 @@
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>@france_boxing_club</t>
+        </is>
+      </c>
       <c r="G419" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -14316,7 +14496,11 @@
           <t>contact.the9boxingclub@gmail.com</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>@the9boxingclub</t>
+        </is>
+      </c>
       <c r="G420" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -14380,10 +14564,14 @@
           <t>contact@shiwatai.com</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>@jittigym</t>
+        </is>
+      </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG handle mismatch, not contacted (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H422" t="inlineStr"/>
@@ -14414,10 +14602,14 @@
           <t>info@syndicate-berlin.de</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>@syndicate_berlin</t>
+        </is>
+      </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H423" t="inlineStr"/>
@@ -14451,7 +14643,7 @@
       <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H424" t="inlineStr"/>
@@ -14516,10 +14708,14 @@
           <t>info@kampfsportschule-berlin.de</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>@evolutionmartialartsberlin</t>
+        </is>
+      </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | IG follow=ok dm=sent (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H426" t="inlineStr"/>
@@ -14651,7 +14847,7 @@
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H430" t="inlineStr"/>
@@ -14780,10 +14976,14 @@
           <t>info@core.university</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>@Core_Martial_Arts_Berlin</t>
+        </is>
+      </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H434" t="inlineStr"/>
@@ -14810,7 +15010,11 @@
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>@kampfkunstschule_neukoelln</t>
+        </is>
+      </c>
       <c r="G435" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -15006,7 +15210,11 @@
           <t>10thplanetberlin@gmail.com</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>@10thplanetberlin</t>
+        </is>
+      </c>
       <c r="G441" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -15043,7 +15251,7 @@
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H442" t="inlineStr"/>
@@ -15074,10 +15282,14 @@
           <t>info@shinzen-dojo.de</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>@shinzendojoberlin</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H443" t="inlineStr"/>
@@ -15111,7 +15323,7 @@
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H444" t="inlineStr"/>
@@ -15444,10 +15656,14 @@
           <t>support@ichigeki.one</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>@ichi_geki__germany</t>
+        </is>
+      </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H454" t="inlineStr"/>
@@ -15508,7 +15724,11 @@
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>@shuriryu_berlin</t>
+        </is>
+      </c>
       <c r="G456" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -15572,10 +15792,14 @@
           <t>info@berlintopteam.de</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>@berlintopteam</t>
+        </is>
+      </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H458" t="inlineStr"/>
@@ -15606,10 +15830,14 @@
           <t>info@bissberlin.de</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>@biss_silat</t>
+        </is>
+      </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H459" t="inlineStr"/>
@@ -15836,10 +16064,14 @@
           <t>info@ikigai-karate-do-berlin.de</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>@ikigai_karate_do_berlin</t>
+        </is>
+      </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=no-msg-btn (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H466" t="inlineStr"/>
@@ -15866,7 +16098,11 @@
         </is>
       </c>
       <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>@kangcenter</t>
+        </is>
+      </c>
       <c r="G467" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -15933,7 +16169,7 @@
       <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H469" t="inlineStr"/>
@@ -16062,7 +16298,11 @@
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>@boxstudio_berlin</t>
+        </is>
+      </c>
       <c r="G473" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -16126,7 +16366,11 @@
           <t>ghostgymberlin@gmail.com</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>@ghostgym__</t>
+        </is>
+      </c>
       <c r="G475" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -16156,7 +16400,11 @@
         </is>
       </c>
       <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>@rollbergerboxgymev</t>
+        </is>
+      </c>
       <c r="G476" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -16193,7 +16441,7 @@
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H477" t="inlineStr"/>
@@ -16227,7 +16475,7 @@
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H478" t="inlineStr"/>
@@ -16356,10 +16604,14 @@
           <t>info@combat-berlin.de</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>@combatberlin</t>
+        </is>
+      </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H482" t="inlineStr"/>
@@ -16390,10 +16642,14 @@
           <t>info@elite-kickboxing.de</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>@elitekickboxinggym</t>
+        </is>
+      </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H483" t="inlineStr"/>
@@ -16672,7 +16928,11 @@
         </is>
       </c>
       <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>@hauptstadtboxen</t>
+        </is>
+      </c>
       <c r="G492" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-23)</t>
@@ -16890,7 +17150,11 @@
         </is>
       </c>
       <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>@adamasjiujitsu</t>
+        </is>
+      </c>
       <c r="G499" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -16954,7 +17218,11 @@
         </is>
       </c>
       <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>@kuksoolwonmadrid</t>
+        </is>
+      </c>
       <c r="G501" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -17474,7 +17742,11 @@
           <t>tomassanchezfitness@gmail.com</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>@tomassanchezfitness</t>
+        </is>
+      </c>
       <c r="G517" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -17606,7 +17878,11 @@
           <t>taekwondokyotovallecas@gmail.com</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>@tkdvallecas</t>
+        </is>
+      </c>
       <c r="G521" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -18232,7 +18508,11 @@
           <t>thewodclub.official@gmail.com</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>@qodeinteractive</t>
+        </is>
+      </c>
       <c r="G540" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -18360,7 +18640,11 @@
           <t>boxeoelrayo@gmail.com</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>@boxeoelrayo</t>
+        </is>
+      </c>
       <c r="G544" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -18906,7 +19190,11 @@
         </is>
       </c>
       <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>@usfitness7</t>
+        </is>
+      </c>
       <c r="G561" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -19094,7 +19382,11 @@
         </is>
       </c>
       <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>@izumi_club</t>
+        </is>
+      </c>
       <c r="G567" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -19154,7 +19446,11 @@
         </is>
       </c>
       <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>@madisonboxing</t>
+        </is>
+      </c>
       <c r="G569" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -19244,7 +19540,11 @@
         </is>
       </c>
       <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>@madisonboxing</t>
+        </is>
+      </c>
       <c r="G572" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -19406,7 +19706,11 @@
         </is>
       </c>
       <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>@angelmorenoboxinggym</t>
+        </is>
+      </c>
       <c r="G577" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -19470,7 +19774,11 @@
           <t>theboxfitandfightclub@gmail.com</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr"/>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>@theboxfitandfightclub</t>
+        </is>
+      </c>
       <c r="G579" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -19606,7 +19914,11 @@
           <t>agboxeo@gmail.com</t>
         </is>
       </c>
-      <c r="F583" t="inlineStr"/>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>@agboxeo</t>
+        </is>
+      </c>
       <c r="G583" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -19900,7 +20212,11 @@
           <t>senshindojobcn@gmail.com</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr"/>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>@senshindojobcn</t>
+        </is>
+      </c>
       <c r="G592" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -20032,7 +20348,11 @@
         </is>
       </c>
       <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>@doyangsal</t>
+        </is>
+      </c>
       <c r="G596" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20126,7 +20446,11 @@
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
-      <c r="F599" t="inlineStr"/>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>@mugendomartialarts</t>
+        </is>
+      </c>
       <c r="G599" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20258,7 +20582,11 @@
           <t>distrito655@hotmail.com</t>
         </is>
       </c>
-      <c r="F603" t="inlineStr"/>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>@billa_barber_shop</t>
+        </is>
+      </c>
       <c r="G603" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -20390,7 +20718,11 @@
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>@shoshinkan_</t>
+        </is>
+      </c>
       <c r="G607" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20420,7 +20752,11 @@
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
-      <c r="F608" t="inlineStr"/>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>@aranha_barcelona</t>
+        </is>
+      </c>
       <c r="G608" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20556,7 +20892,11 @@
           <t>institutodewushu@hotmail.com</t>
         </is>
       </c>
-      <c r="F612" t="inlineStr"/>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>@institutodewushu</t>
+        </is>
+      </c>
       <c r="G612" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL FIXED (multi-address cell -&gt; best valid) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -20586,7 +20926,11 @@
         </is>
       </c>
       <c r="E613" t="inlineStr"/>
-      <c r="F613" t="inlineStr"/>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>@mugendomartialarts</t>
+        </is>
+      </c>
       <c r="G613" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20680,7 +21024,11 @@
         </is>
       </c>
       <c r="E616" t="inlineStr"/>
-      <c r="F616" t="inlineStr"/>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>@kaliflowacademy</t>
+        </is>
+      </c>
       <c r="G616" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20744,7 +21092,11 @@
         </is>
       </c>
       <c r="E618" t="inlineStr"/>
-      <c r="F618" t="inlineStr"/>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>@uft_barcelona</t>
+        </is>
+      </c>
       <c r="G618" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -20872,7 +21224,11 @@
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
-      <c r="F622" t="inlineStr"/>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>@gullojiujitsu</t>
+        </is>
+      </c>
       <c r="G622" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -21038,7 +21394,11 @@
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
-      <c r="F627" t="inlineStr"/>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>@tksbarcelona</t>
+        </is>
+      </c>
       <c r="G627" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -21098,7 +21458,11 @@
         </is>
       </c>
       <c r="E629" t="inlineStr"/>
-      <c r="F629" t="inlineStr"/>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>@KAISARJP</t>
+        </is>
+      </c>
       <c r="G629" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -21226,7 +21590,11 @@
           <t>mmabarcelonateam@gmail.com</t>
         </is>
       </c>
-      <c r="F633" t="inlineStr"/>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>@mmabarcelonateam</t>
+        </is>
+      </c>
       <c r="G633" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -21662,7 +22030,11 @@
         </is>
       </c>
       <c r="E647" t="inlineStr"/>
-      <c r="F647" t="inlineStr"/>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>@belicomunicacion</t>
+        </is>
+      </c>
       <c r="G647" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -21828,7 +22200,11 @@
           <t>humblingjjc@gmail.com</t>
         </is>
       </c>
-      <c r="F652" t="inlineStr"/>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>@humblingjiujitsuclub</t>
+        </is>
+      </c>
       <c r="G652" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -21858,7 +22234,11 @@
         </is>
       </c>
       <c r="E653" t="inlineStr"/>
-      <c r="F653" t="inlineStr"/>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>@antarai_training</t>
+        </is>
+      </c>
       <c r="G653" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -21922,7 +22302,11 @@
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
-      <c r="F655" t="inlineStr"/>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>@wamai_official</t>
+        </is>
+      </c>
       <c r="G655" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -21986,7 +22370,11 @@
         </is>
       </c>
       <c r="E657" t="inlineStr"/>
-      <c r="F657" t="inlineStr"/>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>@mugendomartialarts</t>
+        </is>
+      </c>
       <c r="G657" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -22054,7 +22442,11 @@
           <t>clandestingym@gmail.com</t>
         </is>
       </c>
-      <c r="F659" t="inlineStr"/>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>@clandestinboxinggym</t>
+        </is>
+      </c>
       <c r="G659" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -22114,7 +22506,11 @@
         </is>
       </c>
       <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>@ilionboxing</t>
+        </is>
+      </c>
       <c r="G661" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -22212,7 +22608,11 @@
         </is>
       </c>
       <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>@boxagranprice</t>
+        </is>
+      </c>
       <c r="G664" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-24)</t>
@@ -22766,7 +23166,11 @@
         </is>
       </c>
       <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>@elitekravmagait</t>
+        </is>
+      </c>
       <c r="G681" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -22830,7 +23234,11 @@
         </is>
       </c>
       <c r="E683" t="inlineStr"/>
-      <c r="F683" t="inlineStr"/>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>@asdyamakarateclub</t>
+        </is>
+      </c>
       <c r="G683" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -22924,7 +23332,11 @@
         </is>
       </c>
       <c r="E686" t="inlineStr"/>
-      <c r="F686" t="inlineStr"/>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>@karateclubmartialmilano</t>
+        </is>
+      </c>
       <c r="G686" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -23022,7 +23434,11 @@
           <t>mineirodel@gmail.com</t>
         </is>
       </c>
-      <c r="F689" t="inlineStr"/>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>@team_corallo</t>
+        </is>
+      </c>
       <c r="G689" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -23210,7 +23626,11 @@
         </is>
       </c>
       <c r="E695" t="inlineStr"/>
-      <c r="F695" t="inlineStr"/>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>@divyacenter</t>
+        </is>
+      </c>
       <c r="G695" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -23270,7 +23690,11 @@
         </is>
       </c>
       <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>@dunamisdarsena</t>
+        </is>
+      </c>
       <c r="G697" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -23334,7 +23758,11 @@
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>@accademiakarate</t>
+        </is>
+      </c>
       <c r="G699" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -23394,7 +23822,11 @@
         </is>
       </c>
       <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>@ttraining_milano</t>
+        </is>
+      </c>
       <c r="G701" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -23522,7 +23954,11 @@
         </is>
       </c>
       <c r="E705" t="inlineStr"/>
-      <c r="F705" t="inlineStr"/>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>@dunamisdarsena</t>
+        </is>
+      </c>
       <c r="G705" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -23714,7 +24150,11 @@
         </is>
       </c>
       <c r="E711" t="inlineStr"/>
-      <c r="F711" t="inlineStr"/>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>@voduonggorla</t>
+        </is>
+      </c>
       <c r="G711" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -24008,7 +24448,11 @@
           <t>sharphin.studio@gmail.com</t>
         </is>
       </c>
-      <c r="F720" t="inlineStr"/>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>@sharphin</t>
+        </is>
+      </c>
       <c r="G720" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -24072,7 +24516,11 @@
         </is>
       </c>
       <c r="E722" t="inlineStr"/>
-      <c r="F722" t="inlineStr"/>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>@nino_fit4fightmilano</t>
+        </is>
+      </c>
       <c r="G722" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -24140,7 +24588,11 @@
           <t>dreambelievefight.team@gmail.com</t>
         </is>
       </c>
-      <c r="F724" t="inlineStr"/>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>@dream_believe_fight</t>
+        </is>
+      </c>
       <c r="G724" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -24584,7 +25036,11 @@
         </is>
       </c>
       <c r="E738" t="inlineStr"/>
-      <c r="F738" t="inlineStr"/>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>@montenero_boxing_club</t>
+        </is>
+      </c>
       <c r="G738" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -24828,7 +25284,11 @@
         </is>
       </c>
       <c r="E746" t="inlineStr"/>
-      <c r="F746" t="inlineStr"/>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>@ambrosiana_boxing</t>
+        </is>
+      </c>
       <c r="G746" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -25208,7 +25668,11 @@
         </is>
       </c>
       <c r="E758" t="inlineStr"/>
-      <c r="F758" t="inlineStr"/>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>@bonoacademy</t>
+        </is>
+      </c>
       <c r="G758" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -25656,7 +26120,11 @@
         </is>
       </c>
       <c r="E772" t="inlineStr"/>
-      <c r="F772" t="inlineStr"/>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>@asd_kokorozashi</t>
+        </is>
+      </c>
       <c r="G772" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -25746,7 +26214,11 @@
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
-      <c r="F775" t="inlineStr"/>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>@kendoromahsl</t>
+        </is>
+      </c>
       <c r="G775" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -25780,7 +26252,11 @@
           <t>info.bosacademy@gmail.com</t>
         </is>
       </c>
-      <c r="F776" t="inlineStr"/>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>@bosacademy__</t>
+        </is>
+      </c>
       <c r="G776" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -25848,7 +26324,11 @@
           <t>iltempiodelleartimarziali@live.com</t>
         </is>
       </c>
-      <c r="F778" t="inlineStr"/>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>@tempiodelleartimarzialiroma</t>
+        </is>
+      </c>
       <c r="G778" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -25912,7 +26392,11 @@
           <t>yama.arashi@libero.it</t>
         </is>
       </c>
-      <c r="F780" t="inlineStr"/>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>@yama_arashi_palestra</t>
+        </is>
+      </c>
       <c r="G780" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -26010,7 +26494,11 @@
         </is>
       </c>
       <c r="E783" t="inlineStr"/>
-      <c r="F783" t="inlineStr"/>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>@karate_coreano_tang_soo_do</t>
+        </is>
+      </c>
       <c r="G783" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -26360,7 +26848,11 @@
           <t>dojoitalia@gmail.com</t>
         </is>
       </c>
-      <c r="F794" t="inlineStr"/>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>@dojoitalia</t>
+        </is>
+      </c>
       <c r="G794" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -26420,7 +26912,11 @@
         </is>
       </c>
       <c r="E796" t="inlineStr"/>
-      <c r="F796" t="inlineStr"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>@hungmunmma</t>
+        </is>
+      </c>
       <c r="G796" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -26612,7 +27108,11 @@
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
-      <c r="F802" t="inlineStr"/>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>@shorinji_kempo_italia</t>
+        </is>
+      </c>
       <c r="G802" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -27000,7 +27500,11 @@
           <t>trastevereboxe@gmail.com</t>
         </is>
       </c>
-      <c r="F814" t="inlineStr"/>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>@trastevereboxe</t>
+        </is>
+      </c>
       <c r="G814" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -27132,7 +27636,11 @@
         </is>
       </c>
       <c r="E818" t="inlineStr"/>
-      <c r="F818" t="inlineStr"/>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>@INVICTUSFIGHTCLUB_</t>
+        </is>
+      </c>
       <c r="G818" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -27354,7 +27862,11 @@
         </is>
       </c>
       <c r="E825" t="inlineStr"/>
-      <c r="F825" t="inlineStr"/>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>@palestrauniversalgym</t>
+        </is>
+      </c>
       <c r="G825" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -28058,7 +28570,11 @@
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
-      <c r="F847" t="inlineStr"/>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>@centrodifesaesport</t>
+        </is>
+      </c>
       <c r="G847" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -28284,7 +28800,11 @@
         </is>
       </c>
       <c r="E854" t="inlineStr"/>
-      <c r="F854" t="inlineStr"/>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>@dabliufitnessclub</t>
+        </is>
+      </c>
       <c r="G854" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25)</t>
@@ -29006,7 +29526,11 @@
           <t>leandro.iagher@gmail.com</t>
         </is>
       </c>
-      <c r="F877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>@extremefightersnetwork</t>
+        </is>
+      </c>
       <c r="G877" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25) | EMAIL VERIFIED (webmail, name-matched)</t>
@@ -29292,7 +29816,11 @@
         </is>
       </c>
       <c r="E886" t="inlineStr"/>
-      <c r="F886" t="inlineStr"/>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>@brasaportugal</t>
+        </is>
+      </c>
       <c r="G886" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -29890,7 +30418,11 @@
         </is>
       </c>
       <c r="E905" t="inlineStr"/>
-      <c r="F905" t="inlineStr"/>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>@sthenos.fit</t>
+        </is>
+      </c>
       <c r="G905" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -30018,7 +30550,11 @@
           <t>rounds.academy@gmail.com</t>
         </is>
       </c>
-      <c r="F909" t="inlineStr"/>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>@rounds_academy</t>
+        </is>
+      </c>
       <c r="G909" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -30240,7 +30776,11 @@
         </is>
       </c>
       <c r="E916" t="inlineStr"/>
-      <c r="F916" t="inlineStr"/>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>@graciebarra_pdn</t>
+        </is>
+      </c>
       <c r="G916" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -30368,7 +30908,11 @@
         </is>
       </c>
       <c r="E920" t="inlineStr"/>
-      <c r="F920" t="inlineStr"/>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>@academia_fight_club</t>
+        </is>
+      </c>
       <c r="G920" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -30402,7 +30946,11 @@
           <t>associacaoboxepauloseco@gmail.com</t>
         </is>
       </c>
-      <c r="F921" t="inlineStr"/>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>@paulosecoboxe</t>
+        </is>
+      </c>
       <c r="G921" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -30466,7 +31014,11 @@
           <t>jorgepina.associacao@gmail.com</t>
         </is>
       </c>
-      <c r="F923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>@academia_jorgepina</t>
+        </is>
+      </c>
       <c r="G923" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -30827,7 +31379,7 @@
       <c r="F934" t="inlineStr"/>
       <c r="G934" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H934" t="inlineStr"/>
@@ -31140,7 +31692,11 @@
         </is>
       </c>
       <c r="E944" t="inlineStr"/>
-      <c r="F944" t="inlineStr"/>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>@acmymcalisboa</t>
+        </is>
+      </c>
       <c r="G944" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -31358,7 +31914,11 @@
         </is>
       </c>
       <c r="E951" t="inlineStr"/>
-      <c r="F951" t="inlineStr"/>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>@fitnessfactorypt</t>
+        </is>
+      </c>
       <c r="G951" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -31722,7 +32282,11 @@
         </is>
       </c>
       <c r="E963" t="inlineStr"/>
-      <c r="F963" t="inlineStr"/>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>@five_elements_jiujitsu_lisboa</t>
+        </is>
+      </c>
       <c r="G963" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -31884,7 +32448,11 @@
         </is>
       </c>
       <c r="E968" t="inlineStr"/>
-      <c r="F968" t="inlineStr"/>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>@bitimjiujitsu</t>
+        </is>
+      </c>
       <c r="G968" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -31948,7 +32516,11 @@
         </is>
       </c>
       <c r="E970" t="inlineStr"/>
-      <c r="F970" t="inlineStr"/>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>@taekwondoschweiz</t>
+        </is>
+      </c>
       <c r="G970" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -31978,7 +32550,11 @@
         </is>
       </c>
       <c r="E971" t="inlineStr"/>
-      <c r="F971" t="inlineStr"/>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>@ziranwuyi_kungfu</t>
+        </is>
+      </c>
       <c r="G971" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -32344,10 +32920,14 @@
           <t>info@bjjlab.ch</t>
         </is>
       </c>
-      <c r="F982" t="inlineStr"/>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>@bjjlabzurich</t>
+        </is>
+      </c>
       <c r="G982" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H982" t="inlineStr"/>
@@ -32472,7 +33052,11 @@
         </is>
       </c>
       <c r="E986" t="inlineStr"/>
-      <c r="F986" t="inlineStr"/>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>@tiagobjjdepaula</t>
+        </is>
+      </c>
       <c r="G986" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -32506,7 +33090,11 @@
           <t>adamantiumbjj@gmail.com</t>
         </is>
       </c>
-      <c r="F987" t="inlineStr"/>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>@adamantiumbjjzurich</t>
+        </is>
+      </c>
       <c r="G987" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33078,7 +33666,11 @@
         </is>
       </c>
       <c r="E1005" t="inlineStr"/>
-      <c r="F1005" t="inlineStr"/>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>@kungfuschulesewer</t>
+        </is>
+      </c>
       <c r="G1005" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33108,7 +33700,11 @@
         </is>
       </c>
       <c r="E1006" t="inlineStr"/>
-      <c r="F1006" t="inlineStr"/>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>@mkckickboxingacademy</t>
+        </is>
+      </c>
       <c r="G1006" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33142,7 +33738,11 @@
           <t>fredyminano@hotmail.com</t>
         </is>
       </c>
-      <c r="F1007" t="inlineStr"/>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>@ryueiryu_minano_dojozh</t>
+        </is>
+      </c>
       <c r="G1007" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33244,10 +33844,14 @@
           <t>info@alphamaxbjj.ch</t>
         </is>
       </c>
-      <c r="F1010" t="inlineStr"/>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>@embed.js</t>
+        </is>
+      </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr"/>
@@ -33342,7 +33946,11 @@
           <t>pfluegel007@gmail.com</t>
         </is>
       </c>
-      <c r="F1013" t="inlineStr"/>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>@dreamteamboxing_zuerich</t>
+        </is>
+      </c>
       <c r="G1013" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33674,7 +34282,11 @@
         </is>
       </c>
       <c r="E1023" t="inlineStr"/>
-      <c r="F1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>@jenskrullboxing</t>
+        </is>
+      </c>
       <c r="G1023" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33704,7 +34316,11 @@
         </is>
       </c>
       <c r="E1024" t="inlineStr"/>
-      <c r="F1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>@fightworldzuerich</t>
+        </is>
+      </c>
       <c r="G1024" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -33972,10 +34588,14 @@
           <t>hello@nlsc.ch</t>
         </is>
       </c>
-      <c r="F1032" t="inlineStr"/>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>@nextlevel_sportsclub</t>
+        </is>
+      </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr"/>
@@ -34100,7 +34720,11 @@
         </is>
       </c>
       <c r="E1036" t="inlineStr"/>
-      <c r="F1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>@swiss_budoshop</t>
+        </is>
+      </c>
       <c r="G1036" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
@@ -35098,10 +35722,14 @@
           <t>hooked.hpc@gmail.com</t>
         </is>
       </c>
-      <c r="F1067" t="inlineStr"/>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>@hooked.hpc</t>
+        </is>
+      </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1067" t="inlineStr"/>
@@ -35447,7 +36075,7 @@
       <c r="F1078" t="inlineStr"/>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr"/>
@@ -35474,7 +36102,11 @@
         </is>
       </c>
       <c r="E1079" t="inlineStr"/>
-      <c r="F1079" t="inlineStr"/>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>@stevepowellstudioofselfdefence</t>
+        </is>
+      </c>
       <c r="G1079" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -35508,10 +36140,14 @@
           <t>jamie@hybridmma.academy</t>
         </is>
       </c>
-      <c r="F1080" t="inlineStr"/>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>@hybrid_mma_academy_</t>
+        </is>
+      </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr"/>
@@ -35545,7 +36181,7 @@
       <c r="F1081" t="inlineStr"/>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr"/>
@@ -35639,7 +36275,7 @@
       <c r="F1084" t="inlineStr"/>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1084" t="inlineStr"/>
@@ -35700,10 +36336,14 @@
           <t>info@rakhangmuaythai.co.uk</t>
         </is>
       </c>
-      <c r="F1086" t="inlineStr"/>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>@srmt_singdam</t>
+        </is>
+      </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr"/>
@@ -35734,10 +36374,14 @@
           <t>allpowersgym@outlook.com</t>
         </is>
       </c>
-      <c r="F1087" t="inlineStr"/>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>@allpowersgym</t>
+        </is>
+      </c>
       <c r="G1087" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1087" t="inlineStr"/>
@@ -35768,10 +36412,14 @@
           <t>evademartialarts@gmail.com</t>
         </is>
       </c>
-      <c r="F1088" t="inlineStr"/>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>@evademartialarts</t>
+        </is>
+      </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1088" t="inlineStr"/>
@@ -35802,10 +36450,14 @@
           <t>cherryblossombjj@gmail.com</t>
         </is>
       </c>
-      <c r="F1089" t="inlineStr"/>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>@cherryblossombjj</t>
+        </is>
+      </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr"/>
@@ -35836,10 +36488,14 @@
           <t>manchesterbjj@gmail.com</t>
         </is>
       </c>
-      <c r="F1090" t="inlineStr"/>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>@manchesterbjj</t>
+        </is>
+      </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1090" t="inlineStr"/>
@@ -35896,7 +36552,11 @@
         </is>
       </c>
       <c r="E1092" t="inlineStr"/>
-      <c r="F1092" t="inlineStr"/>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>@manchester_su</t>
+        </is>
+      </c>
       <c r="G1092" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -35933,7 +36593,7 @@
       <c r="F1093" t="inlineStr"/>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1093" t="inlineStr"/>
@@ -35960,7 +36620,11 @@
         </is>
       </c>
       <c r="E1094" t="inlineStr"/>
-      <c r="F1094" t="inlineStr"/>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>@renzogracienh</t>
+        </is>
+      </c>
       <c r="G1094" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -35997,7 +36661,7 @@
       <c r="F1095" t="inlineStr"/>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr"/>
@@ -36024,7 +36688,11 @@
         </is>
       </c>
       <c r="E1096" t="inlineStr"/>
-      <c r="F1096" t="inlineStr"/>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>@dunlaoghairemartialarts</t>
+        </is>
+      </c>
       <c r="G1096" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -36058,10 +36726,14 @@
           <t>hello.ie@brazierjiujitsu.com</t>
         </is>
       </c>
-      <c r="F1097" t="inlineStr"/>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>@brazierjiujitsu</t>
+        </is>
+      </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr"/>
@@ -36126,7 +36798,11 @@
           <t>silverbackjiujitsuacademy@gmail.com</t>
         </is>
       </c>
-      <c r="F1099" t="inlineStr"/>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>@silverback_jiu_jitsu_academy</t>
+        </is>
+      </c>
       <c r="G1099" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -36156,7 +36832,11 @@
         </is>
       </c>
       <c r="E1100" t="inlineStr"/>
-      <c r="F1100" t="inlineStr"/>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>@rgracieireland</t>
+        </is>
+      </c>
       <c r="G1100" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -36190,10 +36870,14 @@
           <t>contact@kravmaga-ireland.com</t>
         </is>
       </c>
-      <c r="F1101" t="inlineStr"/>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>@kravmagabukanireland</t>
+        </is>
+      </c>
       <c r="G1101" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1101" t="inlineStr"/>
@@ -36220,7 +36904,11 @@
         </is>
       </c>
       <c r="E1102" t="inlineStr"/>
-      <c r="F1102" t="inlineStr"/>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>@ucdkarate</t>
+        </is>
+      </c>
       <c r="G1102" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -36250,7 +36938,11 @@
         </is>
       </c>
       <c r="E1103" t="inlineStr"/>
-      <c r="F1103" t="inlineStr"/>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>@stmatthewsboxingclub</t>
+        </is>
+      </c>
       <c r="G1103" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -36280,7 +36972,11 @@
         </is>
       </c>
       <c r="E1104" t="inlineStr"/>
-      <c r="F1104" t="inlineStr"/>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>@blackrockhealthandfitness_</t>
+        </is>
+      </c>
       <c r="G1104" t="inlineStr">
         <is>
           <t>HUNTED (gmaps 2PM 2026-10-26-ammo-topup)</t>
@@ -36317,6 +37013,4422 @@
         </is>
       </c>
       <c r="H1105" t="inlineStr"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>L2026</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Heritage Muay Thai</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>+13468683908</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr"/>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>@heritagemuaythai</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>L2027</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Bam Bam Martial Arts Houston</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>+12815165594</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>help@bambammartialarts.com</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr"/>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>L2028</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Samurai Dojo</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>+18327994595</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>info@samuraihouston.com</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>@houstonsamurai</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>L2029</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Houston Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>+17133645152</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>info@houstonmartialartsacademy.com</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr"/>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>L2030</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Revolution Dojo Houston</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>+18323583958</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr"/>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>@revolution_dojo_houston</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>L2031</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>School of Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>+15056055425</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr"/>
+      <c r="F1111" t="inlineStr"/>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>L2032</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Premier Martial Arts River Oaks</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>+17135818075</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr"/>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>@premiermartialarts</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>L2033</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Houston Karate Academy</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>+17134647937</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr"/>
+      <c r="F1113" t="inlineStr"/>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>L2034</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Midtown MMA Houston</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>+12819744499</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr"/>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>@midtown_mma_houston</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>L2035</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Elite Mixed Martial Arts - Westchase</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>+17133394662</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr"/>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>@elitemmamemorial</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>L2036</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>KEEPMUP martial arts self defense and BJJ</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>+17132927766</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr"/>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>@keepmupmma</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>L2037</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Trein Club</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>+12818886821</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr"/>
+      <c r="F1117" t="inlineStr"/>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>L2038</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>The Garden Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>+18329192349</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr"/>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>@thegardenmartialarts</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>L2039</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Moy Tung Ving Tsun Kung Fu and Martial Arts Center</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>+18328003768</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>houston@txkungfu.com</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr"/>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>L2040</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Elite Mixed Martial Arts - Greenway Plaza/Galleria</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>+18327794319</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr"/>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>@elitemmagreenway</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>L2041</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Premier Martial Arts Houston Heights</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>+17133002421</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr"/>
+      <c r="F1121" t="inlineStr"/>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>L2042</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Legacy Martial Arts &amp; Fitness</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>+18328660412</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr"/>
+      <c r="F1122" t="inlineStr"/>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>L2043</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Millennium Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>+12819874567</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>mma@millenniumma.com</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr"/>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>L2044</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Houston Shaolin Kung Fu Academy</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>+18328583898</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>shaolinacademy18@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr"/>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | EXCLUDED (day13 QA: email not verifiable on the lead own site)</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>L2045</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Urban Jungle Self Defense</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>+17138617252</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>urbanjungle97@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>@urbanjungleselfdefense</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>L2046</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Ronin Mixed Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>+12815428192</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr"/>
+      <c r="F1126" t="inlineStr"/>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>L2047</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Meyerland Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>+17137775425</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>info@meyerlandmartialarts.com</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>@meyerlandmartialarts</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>L2048</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Iron Dragon Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>+17134502555</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr"/>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>@irondragonhouston</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>L2049</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Team Osiris Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>+13466395855</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr"/>
+      <c r="F1129" t="inlineStr"/>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>L2050</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Houston Jujutsu &amp; Kickboxing Academy</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>+17132401316</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr"/>
+      <c r="F1130" t="inlineStr"/>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>L2051</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Elite Mixed Martial Arts - Memorial/Spring Valley</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>+13463364662</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr"/>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>@elitemmamemorial</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>L2052</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Blue Siytangco Taiji Kungfu Academy @ Oriental Phoenix Arts</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>+12817468984</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>orienatlphoenixarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr"/>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>L2053</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>KUNG FU HOUSTON INSTITUTE</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>+18326726666</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr"/>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>@kungfuhouston</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>L2054</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Rilion Gracie Jiu Jitsu Energy Corridor</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>+17132573460</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>riliongraciewesthouston@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>@riliongracieenergycorridor</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>L2055</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>KMA TaeKwonDo Houston</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>+12819205425</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr"/>
+      <c r="F1135" t="inlineStr"/>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>L2056</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Kim Soo Karate, Inc.</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>+17136819261</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>information@kimsookarate.com</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr"/>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>L2057</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Leaders for Life Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>+17137855122</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>leadersforlife.galleria@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>@leadersforlife.galleria</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>L2058</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Shaolin Temple Cultural Center</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>+17132720276</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr"/>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>@shaolintempleculturalcenter</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>L2059</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>USA Karate</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>+12814849006</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr"/>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>@usa_karate1</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>L2060</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Okinawa Karate Center UchinaaDiKan</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>+18328650763</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>info@houstonkarate.org</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>@kyoshi_mcmains</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>L2061</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Bushi Ban Martial Arts &amp; After School Program</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>+12812188989</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>bushibanclearlake@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr"/>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>L2062</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>DefendFit</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>+17132525836</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr"/>
+      <c r="F1142" t="inlineStr"/>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>L2063</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Dragon Gate Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>+18322775205</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>info@dragongatekungfu.com</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr"/>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>L2064</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Tiger-Rock Martial Arts of Houston</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>+12819999078</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr"/>
+      <c r="F1144" t="inlineStr"/>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>L2065</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Grappling Zone</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>+18326685626</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>info@grapplingzone.com</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>@grapplingzone</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>L2066</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Premier Martial Arts Jersey Village</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>+17139133656</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr"/>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>@pmajerseyvillage</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>L2067</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Pablo Silva Brazilian Jiu Jitsu HQ</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>+13463039572</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr"/>
+      <c r="F1147" t="inlineStr"/>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>L2068</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Active Jiu Jitsu Houston</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>+18329741878</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>contact@activejiujitsu.com</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>@activejiujitsu</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>L2069</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Sensei's School of Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>+12817365706</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr"/>
+      <c r="F1149" t="inlineStr"/>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>L2070</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Houston Self Defense</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>+12815680333</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr"/>
+      <c r="F1150" t="inlineStr"/>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>L2071</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Jessie Karate School</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>+17136358447</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr"/>
+      <c r="F1151" t="inlineStr"/>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>L2072</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Wing Chun Kali System Houston</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>+13379440008</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>wingchunkalisystemhouston@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr"/>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>L2073</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Dynamite Muay Thai &amp; Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>+13467022521</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr"/>
+      <c r="F1153" t="inlineStr"/>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>L2074</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Houston Taiji Kungfu Health Academy</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>+17132720018</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr"/>
+      <c r="F1154" t="inlineStr"/>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>L2075</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Level 6 Krav Maga</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>+12816856364</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>dan@level6kravmaga.com</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>@level6kravmaga</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>L2076</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Revolution Dojo</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>+12817551066</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr"/>
+      <c r="F1156" t="inlineStr"/>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>L2077</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Kim's White Tiger</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>+12818071007</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>kimswhitetigertkd@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr"/>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>L2078</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>USA Fight Company</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>+18324585732</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>info@usafightcompany.com</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>@usafightco</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>L2079</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Renzo Gracie Lake Houston</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>+12815000075</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr"/>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>@renzogracielakehouston</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>L2080</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Gracie Barra River Oaks - Jiu Jitsu in Houston TX</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>+12819742544</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>info@gbriveroaks.com</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>@graciebarrariveroaks</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>L2081</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Fast Lane Jiu Jitsu Academy</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>+12818146450</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>fastlanebjjacademy@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>@fastlanejiujitsuacademy</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>L2082</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Inspire Jiu-Jitsu Academy</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>+13463537799</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>info@inspirejiujitsuacademy.com</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>@inspirejiujitsuacademy</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>L2083</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>UFC GYM The Heights</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>+13462351832</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>theheightsgm@ufcgym.com</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>@ufcgym</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG handle mismatch, not contacted (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>L2084</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>4oz Fight Club</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>+18329837355</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr"/>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>@4ozfightclub</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>L2085</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Houston MMA Classes</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>+18323606460</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr"/>
+      <c r="F1165" t="inlineStr"/>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>L2086</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>RISE MMA and Fitness</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>+18325168644</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>info@teamrisemma.com</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>@TEAMRISEMMA</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>L2087</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Team Tooke Mixed Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>+12819557300</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr"/>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>@teamtooke</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>L2088</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>TITLE Boxing Club Chicago Wicker Park</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>+17736616746</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>wickerpark@titleboxingclub.com</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>@titleboxingclub</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>L2089</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Underground Boxing and Conditioning (UBC Gym)</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>+13127259874</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr"/>
+      <c r="F1169" t="inlineStr"/>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>L2090</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Franklin Street Boxing Club</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>+13124220755</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr"/>
+      <c r="F1170" t="inlineStr"/>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>L2091</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Hammer Fitness and Boxing</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>+13125731950</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>info@hammerfitnessandboxing.com</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>@hammerfitnessandboxing</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>L2092</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Title Boxing Club Chicago Lincoln Park</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>+17733277500</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>lincolnpark@titleboxingclub.com</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>@titleboxingclub</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=no-btn dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>L2093</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Dark Horse Gym</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>+17738881643</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>darkhorsegymchicago@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>@darkhorse.boxing</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>L2094</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Windy City Boxing</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>+13126269464</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>info@windycityboxing.com</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>@windycityboxingclub</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>L2095</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Royal Boxing + MMA</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>+13129070467</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>brian@royalboxingmma.com</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr"/>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>L2096</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>One Way Boxing Club</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>+17739715884</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>team@onewayboxingclub.com</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>@onewayboxingclub</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>L2097</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Sam Colonna Boxing</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>+17738476241</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr"/>
+      <c r="F1177" t="inlineStr"/>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>L2098</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Unanimous Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>+17739463315</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr"/>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>@unanimousboxing</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>L2101</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Trenches Boxing &amp; Fitness</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>+17738222496</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr"/>
+      <c r="F1179" t="inlineStr"/>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>L2102</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Chicago Youth Boxing Club</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>+17735654235</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>info@chicagoyouthboxingclub.org</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>@cybc_boxing</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>L2103</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Four Star Fight Club</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>+13128136542</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr"/>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>@4starfight</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>L2104</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Chicago Thai Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>+17732954851</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>info@chicagothaiboxingacademy.com</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>@chicagothaiboxingacademy</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>L2105</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Ayala Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>+17737190369</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr"/>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>@ayalaboxingacademy</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>L2106</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Mission MMA &amp; Fitness</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>+13122852423</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>info@missionmmachicago.com</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>@missionmmachi</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>L2107</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>9Round Kickboxing Fitness</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>+17733601522</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr"/>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>@9roundofficial</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>L2108</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Chicago Fight House</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>+13129759345</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr"/>
+      <c r="F1186" t="inlineStr"/>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>L2109</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>3 Jmh Boxing</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>+17739402014</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>3jmhboxing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>@3jmhboxing</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>L2110</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Benjilany striking - Muay Thai - kickboxing &amp; MMA chicago</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>+13122483843</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr"/>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>@benjilany_striking_chicago</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>L2111</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>1.8.7 Boxing Club llc</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>+17739000187</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr"/>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>@187boxingclub</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>L2112</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Garfield Park Fieldhouse Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>+13127472001</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr"/>
+      <c r="F1190" t="inlineStr"/>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>L2113</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>The Bloc</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>+17736450437</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr"/>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>@theblocchicago</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>L2114</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>UFC GYM Wrigleyville</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>+13312486515</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>wrigleyville@ufcgym.com</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>@ufcgym</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG handle mismatch, not contacted (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>L2115</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Flowers Fitness Club</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>+13124986804</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr"/>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>@flowersfitnessclub1</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>L2116</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>9Round Kickboxing Fitness</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>+13122529909</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr"/>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>@9roundofficial</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>L2117</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Fres Oquendo Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>+13126340036</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr"/>
+      <c r="F1195" t="inlineStr"/>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>L2118</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Fuller Park Fieldhouse Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>+13127476144</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr"/>
+      <c r="F1196" t="inlineStr"/>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>L2119</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>OUT WEST BOXING</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>+17087016203</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr"/>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>@outwestboxing</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>L2121</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Rock Steady Boxing Chicago / Windy City</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>+13124653921</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>info@movement-revolution.com</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>@mvmntrevolution</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG handle mismatch, not contacted (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>L2122</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Champions Factory Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>+17085431076</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>championsfactoryboxing@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr"/>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>L2123</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Clara Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>+13128855934</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr"/>
+      <c r="F1200" t="inlineStr"/>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>L2124</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Hybrid Martial Arts and Fitness</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>+13124200744</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr"/>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>@hybridmartialartschicago</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>L2125</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Chicago School Of Grappling</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>+17734821255</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr"/>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>@chicagoschoolofgrappling</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>L2127</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>9Round Kickboxing Fitness</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>+17736575051</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr"/>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>@9roundlakeview</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>L2128</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Downtown Jiu Jitsu Club Chicago</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>+13125830244</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr"/>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>@downtownjiujitsuclubchicago</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>L2130</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Alphahouse Fitness</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>+13125397944</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr"/>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>@alphahousechicago</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>L2132</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Chicago Fitness Center</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>+17735498181</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>chicagofitnesscenterofficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>@chicagofitnesscenterofficial</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>L2133</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>StrikeFit Chicago</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>+17733057657</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>info@strikefitchicago.com</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>@strikefitchicago</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>L2135</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Viking Muay Thai</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>+15159918009</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr"/>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>@vikingmuaythai</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>L2136</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Muay Thai Chicago Aiki Training Hall</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>+18669988933</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>info@aikitraininghall.com</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>@aiki.training.hall</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>L2137</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Mind Body Defense</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>+17735174992</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr"/>
+      <c r="F1210" t="inlineStr"/>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>L2138</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>SPORT Fitness Chicago</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>+18472041584</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>info@sportfitnesschicago.com</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>@s.p.o.r.t._fitness</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>L2139</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Degerberg Academy of Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>+17737285300</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr"/>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>@degerbergacademy</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>L2140</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>School Of Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>+17735616445</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr"/>
+      <c r="F1213" t="inlineStr"/>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>L2141</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Warrior Institute of Chicago</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>+17733367517</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr"/>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>@wichicago</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>L2142</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Chicago Mixed Martial Arts, South Loop</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>+17734515487</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr"/>
+      <c r="F1215" t="inlineStr"/>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>L2143</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Thousand Waves Martial Arts &amp; Self-Defense Center, NFP</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>+17734727663</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>info@thousandwaves.org</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>@thousandwaveschicago</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>L2144</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Frank's Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>+17086552938</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>franksmartialarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr"/>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>L2145</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Dragon Budo Jujutsu Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>+17086287668</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>dbjmartialarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>@dragon_budo_jujutsu</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>L2146</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Combat Martial Arts / MAI</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>+17736300939</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr"/>
+      <c r="F1219" t="inlineStr"/>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>L2147</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>EKF Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>+17737196488</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr"/>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>@ekfchicago</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>L2148</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Chicago Mixed Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>+13122193095</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr"/>
+      <c r="F1221" t="inlineStr"/>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>L2149</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Imazaki Dojo</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>+13122565484</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>imazakidojo@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr"/>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>L2150</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Chicago Northside Kung Fu</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>+12246005191</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>info@northsidekungfu.com</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>@northsidekungfu</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>L2151</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>White Tiger Martial Arts Chicago</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>+17735495425</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>wtchicago@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr"/>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>L2152</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Fonseca Martial Arts - Roscoe Village</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>+18478660200</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>info@fonsecamartialarts.com</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr"/>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>L2153</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Kung Fu Academy of Chicago</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>+17737618751</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr"/>
+      <c r="F1226" t="inlineStr"/>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>L2154</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Karate Academy</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>+13124166194</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>karateacademyus@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr"/>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>L2155</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Martial Arts Training Temple</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>+17735455490</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr"/>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>@lerasfist</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>L2156</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Yong In Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>+17735861711</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr"/>
+      <c r="F1229" t="inlineStr"/>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>L2157</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Yong In Martial Arts</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>+17737672646</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>yonginmusachicago@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>@yonginmusa</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>L2158</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Redzovic Jiu Jitsu Chicago</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>+17733345189</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>chicagojiujitsu@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr"/>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>L2159</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Woori Taekwondo &amp; Hapkido Academy Chicago</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>+17738779345</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>chicagokma@gmail.com</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr"/>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>L2160</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>TAC Karate &amp; Fitness</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>+17736848500</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr"/>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>@tackaratefitness</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>L2161</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>New Path Wingtsun Kung-fu Sciences</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>+18723482444</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr"/>
+      <c r="F1234" t="inlineStr"/>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>L2162</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Premier Martial Arts West Loop</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>+13128841653</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr"/>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>@premiermartialarts</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -31631,7 +31631,7 @@
       <c r="F942" t="inlineStr"/>
       <c r="G942" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H942" t="inlineStr"/>
@@ -31857,7 +31857,7 @@
       <c r="F949" t="inlineStr"/>
       <c r="G949" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H949" t="inlineStr"/>
@@ -37149,7 +37149,7 @@
       <c r="F1109" t="inlineStr"/>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1109" t="inlineStr"/>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="G1127" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1127" t="inlineStr"/>
@@ -38043,7 +38043,7 @@
       <c r="F1136" t="inlineStr"/>
       <c r="G1136" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1136" t="inlineStr"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="G1140" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | IG profile not found (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1140" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
       <c r="F1143" t="inlineStr"/>
       <c r="G1143" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H1143" t="inlineStr"/>

--- a/WA_Pending_List.xlsx
+++ b/WA_Pending_List.xlsx
@@ -11563,7 +11563,7 @@
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H332" t="inlineStr"/>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched) | IG follow=clicked dm=sent (Daily 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-23) | EMAIL VERIFIED (webmail, name-matched) | IG follow=clicked dm=sent (Daily 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
@@ -33851,7 +33851,7 @@
       </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) | COMPLETE: email sent (Daily 2026-10-27) | IG profile not found (Daily 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-25-ammo-topup) |  | IG profile not found (Daily 2026-10-27) | EMAIL FAILED (Daily 2026-10-27): domain not found (Vera bjj kids)</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr"/>
@@ -37907,7 +37907,7 @@
       <c r="F1132" t="inlineStr"/>
       <c r="G1132" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) | EMAIL FAILED (Daily 2026-10-27): recipient-not-registered (Blue Siytangco Taiji Kungfu)</t>
         </is>
       </c>
       <c r="H1132" t="inlineStr"/>
@@ -39351,7 +39351,7 @@
       </c>
       <c r="G1174" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-27) | COMPLETE: email sent (Daily 2026-10-27) | IG follow=ok dm=sent (Daily 2026-10-27)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-27) |  | IG follow=ok dm=sent (Daily 2026-10-27) | EMAIL FAILED (Daily 2026-10-27): address not found (Windy City Boxing)</t>
         </is>
       </c>
       <c r="H1174" t="inlineStr"/>
